--- a/data/final_data2.xlsx
+++ b/data/final_data2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive\CMIS 4†26 - Project\Data Set\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive\CMIS 4†26 - Project\Data Set\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC972E41-7DBF-4505-A7F0-911B87BB13C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9860EEB-A1CB-4CF8-8031-C20839594F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3037" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3037" uniqueCount="364">
   <si>
     <t>Type of Degree</t>
   </si>
@@ -446,9 +446,6 @@
     <t>Associate Data Engineer</t>
   </si>
   <si>
-    <t>Executive- Sales</t>
-  </si>
-  <si>
     <t>Technical Executive</t>
   </si>
   <si>
@@ -461,9 +458,6 @@
     <t>Associate web engineer</t>
   </si>
   <si>
-    <t>UI/UX Engineer -Intern</t>
-  </si>
-  <si>
     <t>Excellent</t>
   </si>
   <si>
@@ -474,9 +468,6 @@
   </si>
   <si>
     <t>Deen's list academic year 2018/2019</t>
-  </si>
-  <si>
-    <t>Intern- Infrastructure Operations</t>
   </si>
   <si>
     <t>qualified</t>
@@ -608,9 +599,6 @@
     <t>Electronic Engineer</t>
   </si>
   <si>
-    <t>Producion Executive</t>
-  </si>
-  <si>
     <t>software developer</t>
   </si>
   <si>
@@ -650,9 +638,6 @@
     <t xml:space="preserve">In plant trainee </t>
   </si>
   <si>
-    <t>Accountanta executive</t>
-  </si>
-  <si>
     <t>Associate Electronics Engineer</t>
   </si>
   <si>
@@ -660,9 +645,6 @@
   </si>
   <si>
     <t>Instructor</t>
-  </si>
-  <si>
-    <t>Planning - Executive</t>
   </si>
   <si>
     <t>Test Development Engineer</t>
@@ -692,22 +674,13 @@
     <t>Associate Software Engineer</t>
   </si>
   <si>
-    <t>Data Analysists</t>
-  </si>
-  <si>
     <t>Business Analyst</t>
   </si>
   <si>
     <t>Sales &amp; Administration Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Planning cordinator </t>
-  </si>
-  <si>
     <t xml:space="preserve">Sales &amp; Admin Support </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excutive </t>
   </si>
   <si>
     <t>Human Resources Executive</t>
@@ -720,9 +693,6 @@
   </si>
   <si>
     <t>Merchandising Assistant</t>
-  </si>
-  <si>
-    <t>Temporary Demenstration</t>
   </si>
   <si>
     <t xml:space="preserve">Customer Engagement Specialist </t>
@@ -749,13 +719,7 @@
     <t xml:space="preserve">Staff Assistant Gr-(II) </t>
   </si>
   <si>
-    <t>Executive - Process Improvements</t>
-  </si>
-  <si>
     <t>Project Executive</t>
-  </si>
-  <si>
-    <t>Project Cordinator &amp; Site Engineer</t>
   </si>
   <si>
     <t>Junior Software Developer</t>
@@ -767,16 +731,10 @@
     <t>Inspector of Customs</t>
   </si>
   <si>
-    <t>Executive - work Study</t>
-  </si>
-  <si>
     <t>Odoo Development</t>
   </si>
   <si>
     <t>software Engineer</t>
-  </si>
-  <si>
-    <t>Executive - IT</t>
   </si>
   <si>
     <t>Assistant Supervisor</t>
@@ -786,9 +744,6 @@
   </si>
   <si>
     <t>Digital Marketing Analyst</t>
-  </si>
-  <si>
-    <t>Executive - Bulk Merchandiser</t>
   </si>
   <si>
     <t>Executive He &amp;Finance</t>
@@ -809,9 +764,6 @@
     <t>Temparary Tuter</t>
   </si>
   <si>
-    <t>Junior Executive -process</t>
-  </si>
-  <si>
     <t xml:space="preserve">Consultant </t>
   </si>
   <si>
@@ -830,16 +782,10 @@
     <t>Staff Officer</t>
   </si>
   <si>
-    <t>Supply chain - Analyst</t>
-  </si>
-  <si>
     <t>Lab Assistant</t>
   </si>
   <si>
     <t>Sales and administration</t>
-  </si>
-  <si>
-    <t>Executive- QA</t>
   </si>
   <si>
     <t>Tempoary Tuter</t>
@@ -863,9 +809,6 @@
     <t>Executive Project Coordinator</t>
   </si>
   <si>
-    <t>Merchandiser-bulk</t>
-  </si>
-  <si>
     <t>Puchasing Executive</t>
   </si>
   <si>
@@ -873,9 +816,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Executive</t>
-  </si>
-  <si>
-    <t>Executive-Industrial Engineering</t>
   </si>
   <si>
     <t>Operations Analyst</t>
@@ -894,9 +834,6 @@
   </si>
   <si>
     <t>Assistant manager</t>
-  </si>
-  <si>
-    <t>Production Control Unit-Executive</t>
   </si>
   <si>
     <t>Opertions Analyst</t>
@@ -926,9 +863,6 @@
     <t xml:space="preserve">QA engineer </t>
   </si>
   <si>
-    <t>Executive-Human Resourse Development</t>
-  </si>
-  <si>
     <t xml:space="preserve">Associte Software Engineer </t>
   </si>
   <si>
@@ -938,16 +872,10 @@
     <t>Biomedical Service Technical</t>
   </si>
   <si>
-    <t>Executive-Supply chain</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Coordinator </t>
   </si>
   <si>
     <t xml:space="preserve">Engineering Assistant </t>
-  </si>
-  <si>
-    <t>Data Analysis</t>
   </si>
   <si>
     <t>Assocoate Software Engineer</t>
@@ -959,9 +887,6 @@
     <t>Regional Accuracy Analyst</t>
   </si>
   <si>
-    <t>Executive-IE</t>
-  </si>
-  <si>
     <t>Assocrate Web Engineer</t>
   </si>
   <si>
@@ -969,9 +894,6 @@
   </si>
   <si>
     <t>Trainee SEO Specialist</t>
-  </si>
-  <si>
-    <t>Junior Executive-Advance Analytics &amp; Data Translator</t>
   </si>
   <si>
     <t>Engineer Executive</t>
@@ -995,9 +917,6 @@
     <t>Price Analyst</t>
   </si>
   <si>
-    <t>Planning -Executive</t>
-  </si>
-  <si>
     <t>Intern Business analyst</t>
   </si>
   <si>
@@ -1011,9 +930,6 @@
   </si>
   <si>
     <t>Merchandising &amp; planning</t>
-  </si>
-  <si>
-    <t>intern-Quality Engineering</t>
   </si>
   <si>
     <t xml:space="preserve">Quality Assurance Engineer (Associate) </t>
@@ -1035,9 +951,6 @@
   </si>
   <si>
     <t xml:space="preserve">HR officer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">data engineer </t>
   </si>
   <si>
     <t>Material Analyst</t>
@@ -1082,12 +995,6 @@
     <t>business application support</t>
   </si>
   <si>
-    <t xml:space="preserve">business analyst -Intern </t>
-  </si>
-  <si>
-    <t xml:space="preserve">data engineer(Intern) </t>
-  </si>
-  <si>
     <t xml:space="preserve">Research assistant </t>
   </si>
   <si>
@@ -1130,9 +1037,6 @@
     <t>associate application support engineer</t>
   </si>
   <si>
-    <t>Coordinator (Assistant Production)</t>
-  </si>
-  <si>
     <t>Coordinator</t>
   </si>
   <si>
@@ -1149,6 +1053,81 @@
   </si>
   <si>
     <t>Job title</t>
+  </si>
+  <si>
+    <t>intern data engineer</t>
+  </si>
+  <si>
+    <t>Executive Process Improvements</t>
+  </si>
+  <si>
+    <t>Executive work Study</t>
+  </si>
+  <si>
+    <t>Executive IT</t>
+  </si>
+  <si>
+    <t>Executive Bulk Merchandiser</t>
+  </si>
+  <si>
+    <t>Executive QA</t>
+  </si>
+  <si>
+    <t>Executive Industrial Engineering</t>
+  </si>
+  <si>
+    <t>Executive Human Resourse Development</t>
+  </si>
+  <si>
+    <t>Executive Supply chain</t>
+  </si>
+  <si>
+    <t>Executive Sales</t>
+  </si>
+  <si>
+    <t>Executive IE</t>
+  </si>
+  <si>
+    <t>Intern Infrastructure Operations</t>
+  </si>
+  <si>
+    <t>intern Quality Engineering</t>
+  </si>
+  <si>
+    <t>Junior Executive process</t>
+  </si>
+  <si>
+    <t>Supply chain Analyst</t>
+  </si>
+  <si>
+    <t>Merchandiser bulk</t>
+  </si>
+  <si>
+    <t>Production Control Unit Executive</t>
+  </si>
+  <si>
+    <t>Junior Executive Advance Analytics &amp; Data Translator</t>
+  </si>
+  <si>
+    <t>UI/UX Engineer Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business analyst Intern </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinator </t>
+  </si>
+  <si>
+    <t>Planning coordinator</t>
+  </si>
+  <si>
+    <t>Project coordinator &amp; Site Engineer</t>
+  </si>
+  <si>
+    <t>accountant executive</t>
+  </si>
+  <si>
+    <t>executive</t>
   </si>
 </sst>
 </file>
@@ -1519,6 +1498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BI364"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1546,7 +1526,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1558,7 +1538,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
@@ -1636,19 +1616,19 @@
         <v>30</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>32</v>
@@ -1666,19 +1646,19 @@
         <v>36</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>38</v>
@@ -1720,7 +1700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1731,7 +1711,7 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
         <v>54</v>
@@ -1905,7 +1885,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1916,7 +1896,7 @@
         <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
         <v>59</v>
@@ -2090,7 +2070,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -2101,7 +2081,7 @@
         <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E4" t="s">
         <v>59</v>
@@ -2272,7 +2252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -2454,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -2636,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -2647,7 +2627,7 @@
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E7" t="s">
         <v>59</v>
@@ -2818,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -2829,7 +2809,7 @@
         <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E8" t="s">
         <v>59</v>
@@ -2997,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3008,7 +2988,7 @@
         <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E9" t="s">
         <v>59</v>
@@ -3176,7 +3156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -3187,7 +3167,7 @@
         <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="E10" t="s">
         <v>67</v>
@@ -3358,7 +3338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -3540,7 +3520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -3716,7 +3696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -3727,7 +3707,7 @@
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
@@ -3895,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -4077,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -4262,7 +4242,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -4447,7 +4427,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -4626,7 +4606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -4805,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -4816,7 +4796,7 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E19" t="s">
         <v>59</v>
@@ -4984,7 +4964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -5160,7 +5140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -5339,7 +5319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -5518,7 +5498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -5700,7 +5680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -5882,7 +5862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -6064,7 +6044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -6075,7 +6055,7 @@
         <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E26" t="s">
         <v>67</v>
@@ -6243,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -6425,7 +6405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -6436,7 +6416,7 @@
         <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E28" t="s">
         <v>59</v>
@@ -6607,7 +6587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -6618,7 +6598,7 @@
         <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E29" t="s">
         <v>59</v>
@@ -6792,7 +6772,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -6803,7 +6783,7 @@
         <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E30" t="s">
         <v>59</v>
@@ -6974,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>51</v>
       </c>
@@ -6985,7 +6965,7 @@
         <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E31" t="s">
         <v>59</v>
@@ -7156,7 +7136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -7167,7 +7147,7 @@
         <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E32" t="s">
         <v>67</v>
@@ -7341,7 +7321,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>51</v>
       </c>
@@ -7352,7 +7332,7 @@
         <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E33" t="s">
         <v>59</v>
@@ -7523,7 +7503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -7534,7 +7514,7 @@
         <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E34" t="s">
         <v>59</v>
@@ -7705,7 +7685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -7716,7 +7696,7 @@
         <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E35" t="s">
         <v>59</v>
@@ -7887,7 +7867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>51</v>
       </c>
@@ -7898,7 +7878,7 @@
         <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E36" t="s">
         <v>59</v>
@@ -8069,7 +8049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -8080,7 +8060,7 @@
         <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E37" t="s">
         <v>59</v>
@@ -8254,7 +8234,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -8265,7 +8245,7 @@
         <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E38" t="s">
         <v>67</v>
@@ -8436,7 +8416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -8447,7 +8427,7 @@
         <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>204</v>
+        <v>362</v>
       </c>
       <c r="E39" t="s">
         <v>59</v>
@@ -8618,7 +8598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -8794,7 +8774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>65</v>
       </c>
@@ -8805,7 +8785,7 @@
         <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E41" t="s">
         <v>59</v>
@@ -8979,7 +8959,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -8990,7 +8970,7 @@
         <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E42" t="s">
         <v>67</v>
@@ -9161,7 +9141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>65</v>
       </c>
@@ -9340,7 +9320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -9519,7 +9499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>51</v>
       </c>
@@ -9698,7 +9678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -9883,7 +9863,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -10065,7 +10045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -10244,7 +10224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -10423,7 +10403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -10602,7 +10582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -10787,7 +10767,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -10972,7 +10952,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -10983,7 +10963,7 @@
         <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E53" t="s">
         <v>59</v>
@@ -11154,7 +11134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -11165,7 +11145,7 @@
         <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="E54" t="s">
         <v>59</v>
@@ -11333,7 +11313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -11344,7 +11324,7 @@
         <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E55" t="s">
         <v>59</v>
@@ -11515,7 +11495,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -11691,7 +11671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -11702,7 +11682,7 @@
         <v>53</v>
       </c>
       <c r="D57" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E57" t="s">
         <v>67</v>
@@ -11873,7 +11853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>51</v>
       </c>
@@ -11884,7 +11864,7 @@
         <v>53</v>
       </c>
       <c r="D58" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E58" t="s">
         <v>67</v>
@@ -12058,7 +12038,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>51</v>
       </c>
@@ -12069,7 +12049,7 @@
         <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E59" t="s">
         <v>59</v>
@@ -12237,7 +12217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>51</v>
       </c>
@@ -12419,7 +12399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -12604,7 +12584,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>51</v>
       </c>
@@ -12789,7 +12769,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>51</v>
       </c>
@@ -12800,7 +12780,7 @@
         <v>53</v>
       </c>
       <c r="D63" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E63" t="s">
         <v>59</v>
@@ -12968,7 +12948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>51</v>
       </c>
@@ -12979,7 +12959,7 @@
         <v>53</v>
       </c>
       <c r="D64" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E64" t="s">
         <v>59</v>
@@ -13147,7 +13127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>51</v>
       </c>
@@ -13158,7 +13138,7 @@
         <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E65" t="s">
         <v>67</v>
@@ -13329,7 +13309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -13508,7 +13488,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>51</v>
       </c>
@@ -13519,7 +13499,7 @@
         <v>62</v>
       </c>
       <c r="D67" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E67" t="s">
         <v>59</v>
@@ -13690,7 +13670,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="68" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>65</v>
       </c>
@@ -13701,7 +13681,7 @@
         <v>53</v>
       </c>
       <c r="D68" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E68" t="s">
         <v>54</v>
@@ -13872,7 +13852,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="69" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>51</v>
       </c>
@@ -14054,7 +14034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -14065,7 +14045,7 @@
         <v>53</v>
       </c>
       <c r="D70" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E70" t="s">
         <v>59</v>
@@ -14236,7 +14216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>51</v>
       </c>
@@ -14247,7 +14227,7 @@
         <v>71</v>
       </c>
       <c r="D71" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
         <v>67</v>
@@ -14418,7 +14398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>65</v>
       </c>
@@ -14600,7 +14580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>51</v>
       </c>
@@ -14782,7 +14762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>65</v>
       </c>
@@ -14793,7 +14773,7 @@
         <v>71</v>
       </c>
       <c r="D74" t="s">
-        <v>218</v>
+        <v>295</v>
       </c>
       <c r="E74" t="s">
         <v>59</v>
@@ -14961,7 +14941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>65</v>
       </c>
@@ -14972,7 +14952,7 @@
         <v>71</v>
       </c>
       <c r="D75" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E75" t="s">
         <v>67</v>
@@ -15140,7 +15120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>51</v>
       </c>
@@ -15322,7 +15302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>51</v>
       </c>
@@ -15333,7 +15313,7 @@
         <v>53</v>
       </c>
       <c r="D77" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E77" t="s">
         <v>59</v>
@@ -15504,7 +15484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>65</v>
       </c>
@@ -15515,7 +15495,7 @@
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>221</v>
+        <v>360</v>
       </c>
       <c r="E78" t="s">
         <v>69</v>
@@ -15686,7 +15666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>51</v>
       </c>
@@ -15868,7 +15848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>51</v>
       </c>
@@ -16053,7 +16033,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>51</v>
       </c>
@@ -16235,7 +16215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>51</v>
       </c>
@@ -16420,7 +16400,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>51</v>
       </c>
@@ -16431,7 +16411,7 @@
         <v>53</v>
       </c>
       <c r="D83" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E83" t="s">
         <v>59</v>
@@ -16602,7 +16582,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>51</v>
       </c>
@@ -16613,7 +16593,7 @@
         <v>53</v>
       </c>
       <c r="D84" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E84" t="s">
         <v>59</v>
@@ -16784,7 +16764,7 @@
         <v>0</v>
       </c>
       <c r="BI84" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:61" x14ac:dyDescent="0.3">
@@ -16798,7 +16778,7 @@
         <v>62</v>
       </c>
       <c r="D85" t="s">
-        <v>223</v>
+        <v>363</v>
       </c>
       <c r="E85" t="s">
         <v>59</v>
@@ -16966,7 +16946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>51</v>
       </c>
@@ -16977,7 +16957,7 @@
         <v>62</v>
       </c>
       <c r="D86" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E86" t="s">
         <v>59</v>
@@ -17148,7 +17128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>51</v>
       </c>
@@ -17159,7 +17139,7 @@
         <v>62</v>
       </c>
       <c r="D87" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E87" t="s">
         <v>59</v>
@@ -17333,7 +17313,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>51</v>
       </c>
@@ -17512,7 +17492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>51</v>
       </c>
@@ -17691,7 +17671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>51</v>
       </c>
@@ -17702,7 +17682,7 @@
         <v>62</v>
       </c>
       <c r="D90" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="E90" t="s">
         <v>59</v>
@@ -17870,7 +17850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>51</v>
       </c>
@@ -17881,7 +17861,7 @@
         <v>62</v>
       </c>
       <c r="D91" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E91" t="s">
         <v>59</v>
@@ -18055,7 +18035,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="92" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>51</v>
       </c>
@@ -18066,7 +18046,7 @@
         <v>53</v>
       </c>
       <c r="D92" t="s">
-        <v>228</v>
+        <v>95</v>
       </c>
       <c r="E92" t="s">
         <v>69</v>
@@ -18237,7 +18217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>51</v>
       </c>
@@ -18248,7 +18228,7 @@
         <v>62</v>
       </c>
       <c r="D93" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E93" t="s">
         <v>59</v>
@@ -18416,7 +18396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>65</v>
       </c>
@@ -18427,7 +18407,7 @@
         <v>71</v>
       </c>
       <c r="D94" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E94" t="s">
         <v>54</v>
@@ -18598,7 +18578,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="95" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>51</v>
       </c>
@@ -18609,7 +18589,7 @@
         <v>71</v>
       </c>
       <c r="D95" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E95" t="s">
         <v>59</v>
@@ -18780,7 +18760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>65</v>
       </c>
@@ -18791,7 +18771,7 @@
         <v>71</v>
       </c>
       <c r="D96" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E96" t="s">
         <v>67</v>
@@ -18959,7 +18939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>51</v>
       </c>
@@ -19138,7 +19118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>51</v>
       </c>
@@ -19320,7 +19300,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>65</v>
       </c>
@@ -19331,7 +19311,7 @@
         <v>71</v>
       </c>
       <c r="D99" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E99" t="s">
         <v>54</v>
@@ -19502,7 +19482,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>51</v>
       </c>
@@ -19513,7 +19493,7 @@
         <v>53</v>
       </c>
       <c r="D100" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E100" t="s">
         <v>59</v>
@@ -19684,7 +19664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>51</v>
       </c>
@@ -19869,7 +19849,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>51</v>
       </c>
@@ -19880,7 +19860,7 @@
         <v>62</v>
       </c>
       <c r="D102" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="E102" t="s">
         <v>67</v>
@@ -20051,7 +20031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>51</v>
       </c>
@@ -20062,7 +20042,7 @@
         <v>62</v>
       </c>
       <c r="D103" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E103" t="s">
         <v>67</v>
@@ -20233,7 +20213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>51</v>
       </c>
@@ -20244,7 +20224,7 @@
         <v>62</v>
       </c>
       <c r="D104" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="E104" t="s">
         <v>59</v>
@@ -20415,7 +20395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>51</v>
       </c>
@@ -20426,7 +20406,7 @@
         <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E105" t="s">
         <v>59</v>
@@ -20600,7 +20580,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -20611,7 +20591,7 @@
         <v>62</v>
       </c>
       <c r="D106" t="s">
-        <v>237</v>
+        <v>340</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
@@ -20782,7 +20762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>51</v>
       </c>
@@ -20793,7 +20773,7 @@
         <v>62</v>
       </c>
       <c r="D107" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="E107" t="s">
         <v>69</v>
@@ -20967,7 +20947,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>51</v>
       </c>
@@ -21149,7 +21129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>51</v>
       </c>
@@ -21331,7 +21311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>65</v>
       </c>
@@ -21513,7 +21493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>51</v>
       </c>
@@ -21524,7 +21504,7 @@
         <v>62</v>
       </c>
       <c r="D111" t="s">
-        <v>239</v>
+        <v>361</v>
       </c>
       <c r="E111" t="s">
         <v>59</v>
@@ -21695,7 +21675,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>51</v>
       </c>
@@ -21706,7 +21686,7 @@
         <v>62</v>
       </c>
       <c r="D112" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E112" t="s">
         <v>59</v>
@@ -21880,7 +21860,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="113" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>51</v>
       </c>
@@ -22062,7 +22042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>51</v>
       </c>
@@ -22247,7 +22227,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="115" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>51</v>
       </c>
@@ -22426,7 +22406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>65</v>
       </c>
@@ -22611,7 +22591,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="117" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>51</v>
       </c>
@@ -22796,7 +22776,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="118" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>65</v>
       </c>
@@ -22981,7 +22961,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="119" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>51</v>
       </c>
@@ -23163,7 +23143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>65</v>
       </c>
@@ -23345,7 +23325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>65</v>
       </c>
@@ -23527,7 +23507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>51</v>
       </c>
@@ -23712,7 +23692,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="123" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>51</v>
       </c>
@@ -23894,7 +23874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>51</v>
       </c>
@@ -24076,7 +24056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>51</v>
       </c>
@@ -24255,7 +24235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>51</v>
       </c>
@@ -24266,7 +24246,7 @@
         <v>62</v>
       </c>
       <c r="D126" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E126" t="s">
         <v>59</v>
@@ -24437,7 +24417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>65</v>
       </c>
@@ -24613,7 +24593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>65</v>
       </c>
@@ -24789,7 +24769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>65</v>
       </c>
@@ -24800,7 +24780,7 @@
         <v>71</v>
       </c>
       <c r="D129" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E129" t="s">
         <v>59</v>
@@ -24968,7 +24948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>51</v>
       </c>
@@ -25150,7 +25130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>51</v>
       </c>
@@ -25335,7 +25315,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="132" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>51</v>
       </c>
@@ -25514,7 +25494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>51</v>
       </c>
@@ -25696,7 +25676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>65</v>
       </c>
@@ -25872,7 +25852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>65</v>
       </c>
@@ -26051,7 +26031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>51</v>
       </c>
@@ -26062,7 +26042,7 @@
         <v>62</v>
       </c>
       <c r="D136" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="E136" t="s">
         <v>59</v>
@@ -26233,7 +26213,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="137" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>51</v>
       </c>
@@ -26244,7 +26224,7 @@
         <v>62</v>
       </c>
       <c r="D137" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E137" t="s">
         <v>59</v>
@@ -26412,7 +26392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>51</v>
       </c>
@@ -26591,7 +26571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>65</v>
       </c>
@@ -26773,7 +26753,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="140" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>51</v>
       </c>
@@ -26955,7 +26935,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="141" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>51</v>
       </c>
@@ -27137,7 +27117,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="142" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>51</v>
       </c>
@@ -27319,7 +27299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>51</v>
       </c>
@@ -27330,7 +27310,7 @@
         <v>53</v>
       </c>
       <c r="D143" t="s">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="E143" t="s">
         <v>59</v>
@@ -27501,7 +27481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>65</v>
       </c>
@@ -27512,7 +27492,7 @@
         <v>71</v>
       </c>
       <c r="D144" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="E144" t="s">
         <v>54</v>
@@ -27683,7 +27663,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="145" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>51</v>
       </c>
@@ -27862,7 +27842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>51</v>
       </c>
@@ -27873,7 +27853,7 @@
         <v>62</v>
       </c>
       <c r="D146" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="E146" t="s">
         <v>59</v>
@@ -28044,7 +28024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>51</v>
       </c>
@@ -28055,7 +28035,7 @@
         <v>71</v>
       </c>
       <c r="D147" t="s">
-        <v>246</v>
+        <v>342</v>
       </c>
       <c r="E147" t="s">
         <v>59</v>
@@ -28223,7 +28203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>51</v>
       </c>
@@ -28405,7 +28385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>51</v>
       </c>
@@ -28416,7 +28396,7 @@
         <v>62</v>
       </c>
       <c r="D149" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E149" t="s">
         <v>59</v>
@@ -28587,7 +28567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>51</v>
       </c>
@@ -28598,7 +28578,7 @@
         <v>53</v>
       </c>
       <c r="D150" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="E150" t="s">
         <v>59</v>
@@ -28769,7 +28749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>51</v>
       </c>
@@ -28948,7 +28928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>51</v>
       </c>
@@ -29127,7 +29107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>51</v>
       </c>
@@ -29306,7 +29286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>51</v>
       </c>
@@ -29317,7 +29297,7 @@
         <v>62</v>
       </c>
       <c r="D154" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="E154" t="s">
         <v>59</v>
@@ -29488,7 +29468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>51</v>
       </c>
@@ -29499,7 +29479,7 @@
         <v>53</v>
       </c>
       <c r="D155" t="s">
-        <v>250</v>
+        <v>343</v>
       </c>
       <c r="E155" t="s">
         <v>54</v>
@@ -29670,7 +29650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>65</v>
       </c>
@@ -29852,7 +29832,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="157" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>51</v>
       </c>
@@ -29863,7 +29843,7 @@
         <v>62</v>
       </c>
       <c r="D157" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E157" t="s">
         <v>59</v>
@@ -30037,7 +30017,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="158" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>65</v>
       </c>
@@ -30213,7 +30193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>51</v>
       </c>
@@ -30395,7 +30375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>51</v>
       </c>
@@ -30406,7 +30386,7 @@
         <v>62</v>
       </c>
       <c r="D160" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E160" t="s">
         <v>59</v>
@@ -30577,7 +30557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>51</v>
       </c>
@@ -30759,7 +30739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>65</v>
       </c>
@@ -30770,7 +30750,7 @@
         <v>71</v>
       </c>
       <c r="D162" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="E162" t="s">
         <v>59</v>
@@ -30941,7 +30921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>65</v>
       </c>
@@ -30961,7 +30941,7 @@
         <v>72</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H163">
         <v>43200</v>
@@ -31123,7 +31103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>51</v>
       </c>
@@ -31305,7 +31285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>51</v>
       </c>
@@ -31487,7 +31467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>65</v>
       </c>
@@ -31669,7 +31649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>51</v>
       </c>
@@ -31680,7 +31660,7 @@
         <v>71</v>
       </c>
       <c r="D167" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E167" t="s">
         <v>59</v>
@@ -31851,7 +31831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>65</v>
       </c>
@@ -32033,7 +32013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>51</v>
       </c>
@@ -32044,7 +32024,7 @@
         <v>71</v>
       </c>
       <c r="D169" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="E169" t="s">
         <v>59</v>
@@ -32215,7 +32195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>51</v>
       </c>
@@ -32397,7 +32377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>51</v>
       </c>
@@ -32579,7 +32559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>51</v>
       </c>
@@ -32590,7 +32570,7 @@
         <v>53</v>
       </c>
       <c r="D172" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="E172" t="s">
         <v>59</v>
@@ -32761,7 +32741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>51</v>
       </c>
@@ -32772,7 +32752,7 @@
         <v>62</v>
       </c>
       <c r="D173" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E173" t="s">
         <v>59</v>
@@ -32943,7 +32923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>51</v>
       </c>
@@ -32954,7 +32934,7 @@
         <v>71</v>
       </c>
       <c r="D174" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="E174" t="s">
         <v>69</v>
@@ -33125,7 +33105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>51</v>
       </c>
@@ -33136,7 +33116,7 @@
         <v>62</v>
       </c>
       <c r="D175" t="s">
-        <v>257</v>
+        <v>352</v>
       </c>
       <c r="E175" t="s">
         <v>59</v>
@@ -33307,7 +33287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>51</v>
       </c>
@@ -33318,7 +33298,7 @@
         <v>53</v>
       </c>
       <c r="D176" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="E176" t="s">
         <v>54</v>
@@ -33489,7 +33469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>51</v>
       </c>
@@ -33500,7 +33480,7 @@
         <v>53</v>
       </c>
       <c r="D177" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="E177" t="s">
         <v>59</v>
@@ -33668,7 +33648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>51</v>
       </c>
@@ -33679,7 +33659,7 @@
         <v>53</v>
       </c>
       <c r="D178" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="E178" t="s">
         <v>59</v>
@@ -33850,7 +33830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>65</v>
       </c>
@@ -33861,7 +33841,7 @@
         <v>71</v>
       </c>
       <c r="D179" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E179" t="s">
         <v>59</v>
@@ -34029,7 +34009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>51</v>
       </c>
@@ -34211,7 +34191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>51</v>
       </c>
@@ -34222,7 +34202,7 @@
         <v>53</v>
       </c>
       <c r="D181" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="E181" t="s">
         <v>59</v>
@@ -34393,7 +34373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>51</v>
       </c>
@@ -34575,7 +34555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>51</v>
       </c>
@@ -34586,7 +34566,7 @@
         <v>62</v>
       </c>
       <c r="D183" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="E183" t="s">
         <v>59</v>
@@ -34757,7 +34737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>51</v>
       </c>
@@ -34939,7 +34919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>51</v>
       </c>
@@ -34950,7 +34930,7 @@
         <v>62</v>
       </c>
       <c r="D185" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="E185" t="s">
         <v>59</v>
@@ -35121,7 +35101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>51</v>
       </c>
@@ -35303,7 +35283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>51</v>
       </c>
@@ -35314,7 +35294,7 @@
         <v>53</v>
       </c>
       <c r="D187" t="s">
-        <v>264</v>
+        <v>353</v>
       </c>
       <c r="E187" t="s">
         <v>59</v>
@@ -35485,7 +35465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>51</v>
       </c>
@@ -35496,7 +35476,7 @@
         <v>62</v>
       </c>
       <c r="D188" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="E188" t="s">
         <v>54</v>
@@ -35667,7 +35647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>51</v>
       </c>
@@ -35678,7 +35658,7 @@
         <v>62</v>
       </c>
       <c r="D189" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="E189" t="s">
         <v>59</v>
@@ -35849,7 +35829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>51</v>
       </c>
@@ -35860,7 +35840,7 @@
         <v>62</v>
       </c>
       <c r="D190" t="s">
-        <v>267</v>
+        <v>344</v>
       </c>
       <c r="E190" t="s">
         <v>59</v>
@@ -36031,7 +36011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>51</v>
       </c>
@@ -36042,7 +36022,7 @@
         <v>62</v>
       </c>
       <c r="D191" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E191" t="s">
         <v>59</v>
@@ -36213,7 +36193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>51</v>
       </c>
@@ -36395,7 +36375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>51</v>
       </c>
@@ -36577,7 +36557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>65</v>
       </c>
@@ -36588,7 +36568,7 @@
         <v>71</v>
       </c>
       <c r="D194" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="E194" t="s">
         <v>69</v>
@@ -36759,7 +36739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>65</v>
       </c>
@@ -36770,7 +36750,7 @@
         <v>71</v>
       </c>
       <c r="D195" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="E195" t="s">
         <v>69</v>
@@ -36941,7 +36921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>51</v>
       </c>
@@ -36952,7 +36932,7 @@
         <v>62</v>
       </c>
       <c r="D196" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="E196" t="s">
         <v>59</v>
@@ -37120,7 +37100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>65</v>
       </c>
@@ -37131,7 +37111,7 @@
         <v>71</v>
       </c>
       <c r="D197" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="E197" t="s">
         <v>59</v>
@@ -37302,7 +37282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>65</v>
       </c>
@@ -37313,7 +37293,7 @@
         <v>71</v>
       </c>
       <c r="D198" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="E198" t="s">
         <v>59</v>
@@ -37484,7 +37464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>51</v>
       </c>
@@ -37495,7 +37475,7 @@
         <v>62</v>
       </c>
       <c r="D199" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="E199" t="s">
         <v>59</v>
@@ -37663,7 +37643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>65</v>
       </c>
@@ -37674,7 +37654,7 @@
         <v>53</v>
       </c>
       <c r="D200" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="E200" t="s">
         <v>54</v>
@@ -37839,7 +37819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>51</v>
       </c>
@@ -37850,7 +37830,7 @@
         <v>53</v>
       </c>
       <c r="D201" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="E201" t="s">
         <v>59</v>
@@ -38018,7 +37998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>51</v>
       </c>
@@ -38029,7 +38009,7 @@
         <v>62</v>
       </c>
       <c r="D202" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E202" t="s">
         <v>59</v>
@@ -38194,7 +38174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>51</v>
       </c>
@@ -38376,7 +38356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>51</v>
       </c>
@@ -38387,7 +38367,7 @@
         <v>62</v>
       </c>
       <c r="D204" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="E204" t="s">
         <v>59</v>
@@ -38558,7 +38538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>51</v>
       </c>
@@ -38569,7 +38549,7 @@
         <v>62</v>
       </c>
       <c r="D205" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="E205" t="s">
         <v>59</v>
@@ -38740,7 +38720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>51</v>
       </c>
@@ -38751,7 +38731,7 @@
         <v>53</v>
       </c>
       <c r="D206" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="E206" t="s">
         <v>67</v>
@@ -38922,7 +38902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>51</v>
       </c>
@@ -38933,7 +38913,7 @@
         <v>53</v>
       </c>
       <c r="D207" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="E207" t="s">
         <v>59</v>
@@ -39104,7 +39084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>51</v>
       </c>
@@ -39115,7 +39095,7 @@
         <v>53</v>
       </c>
       <c r="D208" t="s">
-        <v>279</v>
+        <v>345</v>
       </c>
       <c r="E208" t="s">
         <v>59</v>
@@ -39286,7 +39266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>51</v>
       </c>
@@ -39297,7 +39277,7 @@
         <v>53</v>
       </c>
       <c r="D209" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E209" t="s">
         <v>59</v>
@@ -39468,7 +39448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>51</v>
       </c>
@@ -39479,7 +39459,7 @@
         <v>62</v>
       </c>
       <c r="D210" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="E210" t="s">
         <v>59</v>
@@ -39647,7 +39627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>51</v>
       </c>
@@ -39658,7 +39638,7 @@
         <v>62</v>
       </c>
       <c r="D211" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E211" t="s">
         <v>59</v>
@@ -39829,7 +39809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>51</v>
       </c>
@@ -40008,7 +39988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>51</v>
       </c>
@@ -40190,7 +40170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>51</v>
       </c>
@@ -40201,7 +40181,7 @@
         <v>62</v>
       </c>
       <c r="D214" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="E214" t="s">
         <v>59</v>
@@ -40369,7 +40349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>51</v>
       </c>
@@ -40551,7 +40531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>51</v>
       </c>
@@ -40562,7 +40542,7 @@
         <v>62</v>
       </c>
       <c r="D216" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="E216" t="s">
         <v>54</v>
@@ -40727,7 +40707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>51</v>
       </c>
@@ -40738,7 +40718,7 @@
         <v>62</v>
       </c>
       <c r="D217" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="E217" t="s">
         <v>59</v>
@@ -40906,7 +40886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>51</v>
       </c>
@@ -40917,7 +40897,7 @@
         <v>62</v>
       </c>
       <c r="D218" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="E218" t="s">
         <v>59</v>
@@ -41088,7 +41068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>51</v>
       </c>
@@ -41270,7 +41250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>51</v>
       </c>
@@ -41281,7 +41261,7 @@
         <v>71</v>
       </c>
       <c r="D220" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
       <c r="E220" t="s">
         <v>59</v>
@@ -41452,7 +41432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>51</v>
       </c>
@@ -41463,7 +41443,7 @@
         <v>71</v>
       </c>
       <c r="D221" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="E221" t="s">
         <v>59</v>
@@ -41634,7 +41614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>65</v>
       </c>
@@ -41645,7 +41625,7 @@
         <v>71</v>
       </c>
       <c r="D222" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="E222" t="s">
         <v>59</v>
@@ -41816,7 +41796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>51</v>
       </c>
@@ -41995,7 +41975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>65</v>
       </c>
@@ -42177,7 +42157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>51</v>
       </c>
@@ -42359,7 +42339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>51</v>
       </c>
@@ -42541,7 +42521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>51</v>
       </c>
@@ -42723,7 +42703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>51</v>
       </c>
@@ -42905,7 +42885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>65</v>
       </c>
@@ -43081,7 +43061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>51</v>
       </c>
@@ -43092,7 +43072,7 @@
         <v>53</v>
       </c>
       <c r="D230" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="E230" t="s">
         <v>59</v>
@@ -43263,7 +43243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>65</v>
       </c>
@@ -43445,7 +43425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>65</v>
       </c>
@@ -43456,7 +43436,7 @@
         <v>75</v>
       </c>
       <c r="D232" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="E232" t="s">
         <v>67</v>
@@ -43627,7 +43607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>51</v>
       </c>
@@ -43638,7 +43618,7 @@
         <v>53</v>
       </c>
       <c r="D233" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E233" t="s">
         <v>59</v>
@@ -43806,7 +43786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>51</v>
       </c>
@@ -43817,7 +43797,7 @@
         <v>71</v>
       </c>
       <c r="D234" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="E234" t="s">
         <v>54</v>
@@ -43988,7 +43968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>51</v>
       </c>
@@ -43999,7 +43979,7 @@
         <v>53</v>
       </c>
       <c r="D235" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="E235" t="s">
         <v>59</v>
@@ -44170,7 +44150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>51</v>
       </c>
@@ -44352,7 +44332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>65</v>
       </c>
@@ -44363,7 +44343,7 @@
         <v>53</v>
       </c>
       <c r="D237" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E237" t="s">
         <v>59</v>
@@ -44534,7 +44514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>51</v>
       </c>
@@ -44713,7 +44693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>65</v>
       </c>
@@ -44895,7 +44875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>51</v>
       </c>
@@ -45074,7 +45054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>51</v>
       </c>
@@ -45085,7 +45065,7 @@
         <v>71</v>
       </c>
       <c r="D241" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="E241" t="s">
         <v>59</v>
@@ -45253,7 +45233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>51</v>
       </c>
@@ -45264,7 +45244,7 @@
         <v>71</v>
       </c>
       <c r="D242" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="E242" t="s">
         <v>59</v>
@@ -45435,7 +45415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>51</v>
       </c>
@@ -45446,7 +45426,7 @@
         <v>53</v>
       </c>
       <c r="D243" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="E243" t="s">
         <v>59</v>
@@ -45617,7 +45597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>51</v>
       </c>
@@ -45796,7 +45776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>51</v>
       </c>
@@ -45807,7 +45787,7 @@
         <v>62</v>
       </c>
       <c r="D245" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="E245" t="s">
         <v>59</v>
@@ -45978,7 +45958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>65</v>
       </c>
@@ -46160,7 +46140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>51</v>
       </c>
@@ -46342,7 +46322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>65</v>
       </c>
@@ -46524,7 +46504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>65</v>
       </c>
@@ -46535,7 +46515,7 @@
         <v>75</v>
       </c>
       <c r="D249" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="E249" t="s">
         <v>59</v>
@@ -46706,7 +46686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>65</v>
       </c>
@@ -46717,7 +46697,7 @@
         <v>71</v>
       </c>
       <c r="D250" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="E250" t="s">
         <v>54</v>
@@ -46888,7 +46868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>51</v>
       </c>
@@ -47070,7 +47050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>51</v>
       </c>
@@ -47081,7 +47061,7 @@
         <v>53</v>
       </c>
       <c r="D252" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="E252" t="s">
         <v>59</v>
@@ -47249,7 +47229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>65</v>
       </c>
@@ -47431,7 +47411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>51</v>
       </c>
@@ -47442,7 +47422,7 @@
         <v>62</v>
       </c>
       <c r="D254" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="E254" t="s">
         <v>59</v>
@@ -47613,7 +47593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>51</v>
       </c>
@@ -47624,7 +47604,7 @@
         <v>62</v>
       </c>
       <c r="D255" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="E255" t="s">
         <v>59</v>
@@ -47795,7 +47775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>65</v>
       </c>
@@ -47806,7 +47786,7 @@
         <v>71</v>
       </c>
       <c r="D256" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="E256" t="s">
         <v>59</v>
@@ -47977,7 +47957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>51</v>
       </c>
@@ -47988,7 +47968,7 @@
         <v>71</v>
       </c>
       <c r="D257" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="E257" t="s">
         <v>59</v>
@@ -48159,7 +48139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>65</v>
       </c>
@@ -48170,7 +48150,7 @@
         <v>71</v>
       </c>
       <c r="D258" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="E258" t="s">
         <v>59</v>
@@ -48341,7 +48321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>65</v>
       </c>
@@ -48352,7 +48332,7 @@
         <v>75</v>
       </c>
       <c r="D259" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="E259" t="s">
         <v>59</v>
@@ -48523,7 +48503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>65</v>
       </c>
@@ -48534,7 +48514,7 @@
         <v>71</v>
       </c>
       <c r="D260" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="E260" t="s">
         <v>59</v>
@@ -48705,7 +48685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>51</v>
       </c>
@@ -48716,7 +48696,7 @@
         <v>62</v>
       </c>
       <c r="D261" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="E261" t="s">
         <v>59</v>
@@ -48884,7 +48864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>51</v>
       </c>
@@ -48895,7 +48875,7 @@
         <v>53</v>
       </c>
       <c r="D262" t="s">
-        <v>136</v>
+        <v>348</v>
       </c>
       <c r="E262" t="s">
         <v>59</v>
@@ -49063,7 +49043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>51</v>
       </c>
@@ -49074,7 +49054,7 @@
         <v>62</v>
       </c>
       <c r="D263" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="E263" t="s">
         <v>59</v>
@@ -49242,7 +49222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>51</v>
       </c>
@@ -49253,7 +49233,7 @@
         <v>62</v>
       </c>
       <c r="D264" t="s">
-        <v>307</v>
+        <v>349</v>
       </c>
       <c r="E264" t="s">
         <v>59</v>
@@ -49421,7 +49401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>51</v>
       </c>
@@ -49432,7 +49412,7 @@
         <v>71</v>
       </c>
       <c r="D265" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="E265" t="s">
         <v>59</v>
@@ -49603,7 +49583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>51</v>
       </c>
@@ -49614,7 +49594,7 @@
         <v>62</v>
       </c>
       <c r="D266" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="E266" t="s">
         <v>67</v>
@@ -49785,7 +49765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>51</v>
       </c>
@@ -49796,7 +49776,7 @@
         <v>62</v>
       </c>
       <c r="D267" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="E267" t="s">
         <v>59</v>
@@ -49964,7 +49944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>51</v>
       </c>
@@ -50146,7 +50126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>51</v>
       </c>
@@ -50157,7 +50137,7 @@
         <v>71</v>
       </c>
       <c r="D269" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="E269" t="s">
         <v>59</v>
@@ -50328,7 +50308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>65</v>
       </c>
@@ -50339,7 +50319,7 @@
         <v>75</v>
       </c>
       <c r="D270" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E270" t="s">
         <v>59</v>
@@ -50510,7 +50490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>51</v>
       </c>
@@ -50521,7 +50501,7 @@
         <v>62</v>
       </c>
       <c r="D271" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="E271" t="s">
         <v>67</v>
@@ -50692,7 +50672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>51</v>
       </c>
@@ -50703,7 +50683,7 @@
         <v>71</v>
       </c>
       <c r="D272" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E272" t="s">
         <v>67</v>
@@ -50874,7 +50854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>51</v>
       </c>
@@ -50885,7 +50865,7 @@
         <v>71</v>
       </c>
       <c r="D273" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E273" t="s">
         <v>69</v>
@@ -51053,7 +51033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>65</v>
       </c>
@@ -51064,7 +51044,7 @@
         <v>71</v>
       </c>
       <c r="D274" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="E274" t="s">
         <v>59</v>
@@ -51235,7 +51215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>51</v>
       </c>
@@ -51246,7 +51226,7 @@
         <v>53</v>
       </c>
       <c r="D275" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="E275" t="s">
         <v>59</v>
@@ -51417,7 +51397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>65</v>
       </c>
@@ -51428,7 +51408,7 @@
         <v>71</v>
       </c>
       <c r="D276" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
@@ -51599,7 +51579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>51</v>
       </c>
@@ -51610,7 +51590,7 @@
         <v>62</v>
       </c>
       <c r="D277" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="E277" t="s">
         <v>59</v>
@@ -51775,7 +51755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>51</v>
       </c>
@@ -51957,7 +51937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>65</v>
       </c>
@@ -52136,7 +52116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>51</v>
       </c>
@@ -52147,7 +52127,7 @@
         <v>62</v>
       </c>
       <c r="D280" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E280" t="s">
         <v>59</v>
@@ -52315,7 +52295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>51</v>
       </c>
@@ -52326,7 +52306,7 @@
         <v>53</v>
       </c>
       <c r="D281" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="E281" t="s">
         <v>59</v>
@@ -52494,7 +52474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>65</v>
       </c>
@@ -52676,7 +52656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>65</v>
       </c>
@@ -52687,7 +52667,7 @@
         <v>71</v>
       </c>
       <c r="D283" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E283" t="s">
         <v>69</v>
@@ -52858,7 +52838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>51</v>
       </c>
@@ -53040,7 +53020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>65</v>
       </c>
@@ -53222,7 +53202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>51</v>
       </c>
@@ -53233,7 +53213,7 @@
         <v>53</v>
       </c>
       <c r="D286" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E286" t="s">
         <v>59</v>
@@ -53404,7 +53384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>51</v>
       </c>
@@ -53415,7 +53395,7 @@
         <v>53</v>
       </c>
       <c r="D287" t="s">
-        <v>141</v>
+        <v>357</v>
       </c>
       <c r="E287" t="s">
         <v>67</v>
@@ -53586,7 +53566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>51</v>
       </c>
@@ -53597,7 +53577,7 @@
         <v>53</v>
       </c>
       <c r="D288" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="E288" t="s">
         <v>54</v>
@@ -53768,7 +53748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>51</v>
       </c>
@@ -53779,7 +53759,7 @@
         <v>53</v>
       </c>
       <c r="D289" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="E289" t="s">
         <v>59</v>
@@ -53929,7 +53909,7 @@
         <v>56</v>
       </c>
       <c r="BB289" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC289">
         <v>0</v>
@@ -53950,7 +53930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>51</v>
       </c>
@@ -53961,7 +53941,7 @@
         <v>53</v>
       </c>
       <c r="D290" t="s">
-        <v>319</v>
+        <v>116</v>
       </c>
       <c r="E290" t="s">
         <v>59</v>
@@ -54111,7 +54091,7 @@
         <v>60</v>
       </c>
       <c r="BB290" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC290">
         <v>1</v>
@@ -54132,7 +54112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>65</v>
       </c>
@@ -54314,7 +54294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>51</v>
       </c>
@@ -54325,7 +54305,7 @@
         <v>71</v>
       </c>
       <c r="D292" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E292" t="s">
         <v>59</v>
@@ -54472,7 +54452,7 @@
         <v>0</v>
       </c>
       <c r="BA292" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB292" t="s">
         <v>60</v>
@@ -54496,7 +54476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>51</v>
       </c>
@@ -54507,7 +54487,7 @@
         <v>71</v>
       </c>
       <c r="D293" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="E293" t="s">
         <v>54</v>
@@ -54654,7 +54634,7 @@
         <v>60</v>
       </c>
       <c r="BB293" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC293">
         <v>1</v>
@@ -54675,10 +54655,10 @@
         <v>1</v>
       </c>
       <c r="BI293" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
-    <row r="294" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>65</v>
       </c>
@@ -54689,7 +54669,7 @@
         <v>53</v>
       </c>
       <c r="D294" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="E294" t="s">
         <v>59</v>
@@ -54860,10 +54840,10 @@
         <v>0</v>
       </c>
       <c r="BI294" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="295" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>51</v>
       </c>
@@ -54874,7 +54854,7 @@
         <v>53</v>
       </c>
       <c r="D295" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="E295" t="s">
         <v>54</v>
@@ -55045,7 +55025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>51</v>
       </c>
@@ -55056,7 +55036,7 @@
         <v>53</v>
       </c>
       <c r="D296" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="E296" t="s">
         <v>59</v>
@@ -55224,7 +55204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>51</v>
       </c>
@@ -55235,7 +55215,7 @@
         <v>53</v>
       </c>
       <c r="D297" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="E297" t="s">
         <v>69</v>
@@ -55403,10 +55383,10 @@
         <v>0</v>
       </c>
       <c r="BI297" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="298" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>51</v>
       </c>
@@ -55417,7 +55397,7 @@
         <v>53</v>
       </c>
       <c r="D298" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="E298" t="s">
         <v>59</v>
@@ -55585,10 +55565,10 @@
         <v>0</v>
       </c>
       <c r="BI298" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
-    <row r="299" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>51</v>
       </c>
@@ -55599,7 +55579,7 @@
         <v>53</v>
       </c>
       <c r="D299" t="s">
-        <v>146</v>
+        <v>350</v>
       </c>
       <c r="E299" t="s">
         <v>67</v>
@@ -55746,10 +55726,10 @@
         <v>0</v>
       </c>
       <c r="BA299" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB299" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC299">
         <v>1</v>
@@ -55770,7 +55750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>51</v>
       </c>
@@ -55781,7 +55761,7 @@
         <v>53</v>
       </c>
       <c r="D300" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="E300" t="s">
         <v>67</v>
@@ -55949,10 +55929,10 @@
         <v>0</v>
       </c>
       <c r="BI300" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="301" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>51</v>
       </c>
@@ -55963,7 +55943,7 @@
         <v>53</v>
       </c>
       <c r="D301" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="E301" t="s">
         <v>59</v>
@@ -56134,7 +56114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>51</v>
       </c>
@@ -56145,7 +56125,7 @@
         <v>53</v>
       </c>
       <c r="D302" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="E302" t="s">
         <v>59</v>
@@ -56316,7 +56296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>65</v>
       </c>
@@ -56327,7 +56307,7 @@
         <v>71</v>
       </c>
       <c r="D303" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E303" t="s">
         <v>59</v>
@@ -56477,7 +56457,7 @@
         <v>60</v>
       </c>
       <c r="BB303" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC303">
         <v>0</v>
@@ -56498,7 +56478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>51</v>
       </c>
@@ -56509,7 +56489,7 @@
         <v>53</v>
       </c>
       <c r="D304" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="E304" t="s">
         <v>67</v>
@@ -56680,7 +56660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>51</v>
       </c>
@@ -56691,7 +56671,7 @@
         <v>71</v>
       </c>
       <c r="D305" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
       <c r="E305" t="s">
         <v>59</v>
@@ -56862,7 +56842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>51</v>
       </c>
@@ -56873,7 +56853,7 @@
         <v>53</v>
       </c>
       <c r="D306" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="E306" t="s">
         <v>67</v>
@@ -57044,7 +57024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>65</v>
       </c>
@@ -57055,7 +57035,7 @@
         <v>71</v>
       </c>
       <c r="D307" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="E307" t="s">
         <v>59</v>
@@ -57226,7 +57206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>51</v>
       </c>
@@ -57237,7 +57217,7 @@
         <v>71</v>
       </c>
       <c r="D308" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="E308" t="s">
         <v>59</v>
@@ -57408,10 +57388,10 @@
         <v>0</v>
       </c>
       <c r="BI308" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="309" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>65</v>
       </c>
@@ -57422,7 +57402,7 @@
         <v>71</v>
       </c>
       <c r="D309" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="E309" t="s">
         <v>59</v>
@@ -57590,7 +57570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>65</v>
       </c>
@@ -57772,7 +57752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>65</v>
       </c>
@@ -57954,7 +57934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>51</v>
       </c>
@@ -57965,7 +57945,7 @@
         <v>53</v>
       </c>
       <c r="D312" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="E312" t="s">
         <v>59</v>
@@ -58136,7 +58116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>51</v>
       </c>
@@ -58147,7 +58127,7 @@
         <v>53</v>
       </c>
       <c r="D313" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="E313" t="s">
         <v>54</v>
@@ -58312,7 +58292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>51</v>
       </c>
@@ -58323,7 +58303,7 @@
         <v>53</v>
       </c>
       <c r="D314" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="E314" t="s">
         <v>59</v>
@@ -58494,7 +58474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>51</v>
       </c>
@@ -58505,7 +58485,7 @@
         <v>53</v>
       </c>
       <c r="D315" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E315" t="s">
         <v>67</v>
@@ -58673,7 +58653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>51</v>
       </c>
@@ -58684,7 +58664,7 @@
         <v>71</v>
       </c>
       <c r="D316" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E316" t="s">
         <v>59</v>
@@ -58855,7 +58835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>65</v>
       </c>
@@ -58866,7 +58846,7 @@
         <v>71</v>
       </c>
       <c r="D317" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="E317" t="s">
         <v>59</v>
@@ -59010,10 +58990,10 @@
         <v>0</v>
       </c>
       <c r="BA317" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB317" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC317">
         <v>1</v>
@@ -59034,7 +59014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>65</v>
       </c>
@@ -59045,7 +59025,7 @@
         <v>71</v>
       </c>
       <c r="D318" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="E318" t="s">
         <v>59</v>
@@ -59213,10 +59193,10 @@
         <v>0</v>
       </c>
       <c r="BI318" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="319" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>51</v>
       </c>
@@ -59227,7 +59207,7 @@
         <v>53</v>
       </c>
       <c r="D319" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="E319" t="s">
         <v>59</v>
@@ -59398,7 +59378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>65</v>
       </c>
@@ -59409,7 +59389,7 @@
         <v>71</v>
       </c>
       <c r="D320" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="E320" t="s">
         <v>59</v>
@@ -59577,10 +59557,10 @@
         <v>0</v>
       </c>
       <c r="BI320" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
-    <row r="321" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>51</v>
       </c>
@@ -59591,7 +59571,7 @@
         <v>53</v>
       </c>
       <c r="D321" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E321" t="s">
         <v>59</v>
@@ -59759,7 +59739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>51</v>
       </c>
@@ -59770,7 +59750,7 @@
         <v>53</v>
       </c>
       <c r="D322" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="E322" t="s">
         <v>59</v>
@@ -59938,7 +59918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>65</v>
       </c>
@@ -59949,7 +59929,7 @@
         <v>71</v>
       </c>
       <c r="D323" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="E323" t="s">
         <v>54</v>
@@ -60096,7 +60076,7 @@
         <v>60</v>
       </c>
       <c r="BB323" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC323">
         <v>1</v>
@@ -60117,10 +60097,10 @@
         <v>1</v>
       </c>
       <c r="BI323" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="324" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>51</v>
       </c>
@@ -60131,7 +60111,7 @@
         <v>53</v>
       </c>
       <c r="D324" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E324" t="s">
         <v>59</v>
@@ -60302,7 +60282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>51</v>
       </c>
@@ -60313,7 +60293,7 @@
         <v>53</v>
       </c>
       <c r="D325" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="E325" t="s">
         <v>54</v>
@@ -60484,7 +60464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>65</v>
       </c>
@@ -60495,7 +60475,7 @@
         <v>71</v>
       </c>
       <c r="D326" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="E326" t="s">
         <v>59</v>
@@ -60642,10 +60622,10 @@
         <v>0</v>
       </c>
       <c r="BA326" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB326" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC326">
         <v>1</v>
@@ -60666,7 +60646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>51</v>
       </c>
@@ -60677,7 +60657,7 @@
         <v>53</v>
       </c>
       <c r="D327" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="E327" t="s">
         <v>59</v>
@@ -60824,10 +60804,10 @@
         <v>0</v>
       </c>
       <c r="BA327" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB327" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC327">
         <v>1</v>
@@ -60848,7 +60828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>51</v>
       </c>
@@ -60859,7 +60839,7 @@
         <v>53</v>
       </c>
       <c r="D328" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="E328" t="s">
         <v>59</v>
@@ -61006,10 +60986,10 @@
         <v>0</v>
       </c>
       <c r="BA328" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB328" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC328">
         <v>1</v>
@@ -61030,7 +61010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>51</v>
       </c>
@@ -61041,7 +61021,7 @@
         <v>71</v>
       </c>
       <c r="D329" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="E329" t="s">
         <v>59</v>
@@ -61188,10 +61168,10 @@
         <v>0</v>
       </c>
       <c r="BA329" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB329" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC329">
         <v>1</v>
@@ -61212,10 +61192,10 @@
         <v>1</v>
       </c>
       <c r="BI329" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
-    <row r="330" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>51</v>
       </c>
@@ -61226,7 +61206,7 @@
         <v>53</v>
       </c>
       <c r="D330" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="E330" t="s">
         <v>59</v>
@@ -61394,10 +61374,10 @@
         <v>0</v>
       </c>
       <c r="BI330" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="331" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>51</v>
       </c>
@@ -61408,7 +61388,7 @@
         <v>71</v>
       </c>
       <c r="D331" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="E331" t="s">
         <v>67</v>
@@ -61579,10 +61559,10 @@
         <v>0</v>
       </c>
       <c r="BI331" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
-    <row r="332" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>51</v>
       </c>
@@ -61593,7 +61573,7 @@
         <v>53</v>
       </c>
       <c r="D332" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E332" t="s">
         <v>59</v>
@@ -61764,7 +61744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>65</v>
       </c>
@@ -61775,7 +61755,7 @@
         <v>75</v>
       </c>
       <c r="D333" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E333" t="s">
         <v>67</v>
@@ -61946,7 +61926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>65</v>
       </c>
@@ -61957,7 +61937,7 @@
         <v>71</v>
       </c>
       <c r="D334" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="E334" t="s">
         <v>54</v>
@@ -62122,7 +62102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>65</v>
       </c>
@@ -62133,7 +62113,7 @@
         <v>71</v>
       </c>
       <c r="D335" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E335" t="s">
         <v>59</v>
@@ -62304,10 +62284,10 @@
         <v>0</v>
       </c>
       <c r="BI335" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="336" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>65</v>
       </c>
@@ -62318,7 +62298,7 @@
         <v>53</v>
       </c>
       <c r="D336" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E336" t="s">
         <v>59</v>
@@ -62489,10 +62469,10 @@
         <v>0</v>
       </c>
       <c r="BI336" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="337" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>65</v>
       </c>
@@ -62503,7 +62483,7 @@
         <v>71</v>
       </c>
       <c r="D337" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="E337" t="s">
         <v>59</v>
@@ -62674,7 +62654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>65</v>
       </c>
@@ -62685,7 +62665,7 @@
         <v>71</v>
       </c>
       <c r="D338" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="E338" t="s">
         <v>69</v>
@@ -62856,7 +62836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>65</v>
       </c>
@@ -62867,7 +62847,7 @@
         <v>71</v>
       </c>
       <c r="D339" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="E339" t="s">
         <v>59</v>
@@ -63035,10 +63015,10 @@
         <v>0</v>
       </c>
       <c r="BI339" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="340" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>51</v>
       </c>
@@ -63049,7 +63029,7 @@
         <v>53</v>
       </c>
       <c r="D340" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="E340" t="s">
         <v>59</v>
@@ -63220,7 +63200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>51</v>
       </c>
@@ -63231,7 +63211,7 @@
         <v>53</v>
       </c>
       <c r="D341" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="E341" t="s">
         <v>59</v>
@@ -63402,7 +63382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>65</v>
       </c>
@@ -63578,7 +63558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>51</v>
       </c>
@@ -63589,7 +63569,7 @@
         <v>53</v>
       </c>
       <c r="D343" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="E343" t="s">
         <v>54</v>
@@ -63754,7 +63734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>65</v>
       </c>
@@ -63765,7 +63745,7 @@
         <v>71</v>
       </c>
       <c r="D344" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="E344" t="s">
         <v>59</v>
@@ -63936,7 +63916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>65</v>
       </c>
@@ -63947,7 +63927,7 @@
         <v>71</v>
       </c>
       <c r="D345" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="E345" t="s">
         <v>59</v>
@@ -64094,7 +64074,7 @@
         <v>60</v>
       </c>
       <c r="BB345" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC345">
         <v>1</v>
@@ -64115,10 +64095,10 @@
         <v>0</v>
       </c>
       <c r="BI345" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="346" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>51</v>
       </c>
@@ -64129,7 +64109,7 @@
         <v>53</v>
       </c>
       <c r="D346" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="E346" t="s">
         <v>59</v>
@@ -64300,10 +64280,10 @@
         <v>1</v>
       </c>
       <c r="BI346" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="347" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>51</v>
       </c>
@@ -64485,10 +64465,10 @@
         <v>0</v>
       </c>
       <c r="BI347" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="348" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>65</v>
       </c>
@@ -64499,7 +64479,7 @@
         <v>71</v>
       </c>
       <c r="D348" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="E348" t="s">
         <v>59</v>
@@ -64670,7 +64650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>51</v>
       </c>
@@ -64852,7 +64832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>51</v>
       </c>
@@ -65034,7 +65014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>65</v>
       </c>
@@ -65192,7 +65172,7 @@
         <v>0</v>
       </c>
       <c r="BA351" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB351" t="s">
         <v>60</v>
@@ -65216,10 +65196,10 @@
         <v>0</v>
       </c>
       <c r="BI351" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="352" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>65</v>
       </c>
@@ -65230,7 +65210,7 @@
         <v>71</v>
       </c>
       <c r="D352" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="E352" t="s">
         <v>59</v>
@@ -65371,10 +65351,10 @@
         <v>0</v>
       </c>
       <c r="BA352" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BB352" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC352">
         <v>0</v>
@@ -65395,7 +65375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>51</v>
       </c>
@@ -65406,7 +65386,7 @@
         <v>71</v>
       </c>
       <c r="D353" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="E353" t="s">
         <v>54</v>
@@ -65556,7 +65536,7 @@
         <v>60</v>
       </c>
       <c r="BB353" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC353">
         <v>0</v>
@@ -65577,10 +65557,10 @@
         <v>0</v>
       </c>
       <c r="BI353" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="354" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>65</v>
       </c>
@@ -65591,7 +65571,7 @@
         <v>71</v>
       </c>
       <c r="D354" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="E354" t="s">
         <v>59</v>
@@ -65759,10 +65739,10 @@
         <v>0</v>
       </c>
       <c r="BI354" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
-    <row r="355" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>51</v>
       </c>
@@ -65773,7 +65753,7 @@
         <v>71</v>
       </c>
       <c r="D355" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="E355" t="s">
         <v>59</v>
@@ -65944,7 +65924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>65</v>
       </c>
@@ -65955,7 +65935,7 @@
         <v>71</v>
       </c>
       <c r="D356" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="E356" t="s">
         <v>59</v>
@@ -66123,10 +66103,10 @@
         <v>0</v>
       </c>
       <c r="BI356" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="357" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>65</v>
       </c>
@@ -66137,7 +66117,7 @@
         <v>75</v>
       </c>
       <c r="D357" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="E357" t="s">
         <v>54</v>
@@ -66287,7 +66267,7 @@
         <v>60</v>
       </c>
       <c r="BB357" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC357">
         <v>1</v>
@@ -66308,7 +66288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>65</v>
       </c>
@@ -66319,7 +66299,7 @@
         <v>71</v>
       </c>
       <c r="D358" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="E358" t="s">
         <v>59</v>
@@ -66490,10 +66470,10 @@
         <v>0</v>
       </c>
       <c r="BI358" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="359" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>51</v>
       </c>
@@ -66675,10 +66655,10 @@
         <v>0</v>
       </c>
       <c r="BI359" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="360" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>65</v>
       </c>
@@ -66689,7 +66669,7 @@
         <v>75</v>
       </c>
       <c r="D360" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="E360" t="s">
         <v>69</v>
@@ -66860,10 +66840,10 @@
         <v>1</v>
       </c>
       <c r="BI360" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="361" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>65</v>
       </c>
@@ -67024,7 +67004,7 @@
         <v>60</v>
       </c>
       <c r="BB361" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC361">
         <v>1</v>
@@ -67045,7 +67025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>65</v>
       </c>
@@ -67206,7 +67186,7 @@
         <v>60</v>
       </c>
       <c r="BB362" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BC362">
         <v>1</v>
@@ -67227,10 +67207,10 @@
         <v>1</v>
       </c>
       <c r="BI362" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="363" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>65</v>
       </c>
@@ -67412,7 +67392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>65</v>
       </c>
@@ -67595,7 +67575,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI364" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BI364" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Excutive"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/final_data2.xlsx
+++ b/data/final_data2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive\CMIS 4†26 - Project\Data Set\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A77D938-8F82-46EF-87F0-41B60C8E7585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7344F006-EBEC-49AA-B6B2-6F56D144A98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="330">
   <si>
     <t>Type of Degree</t>
   </si>
@@ -920,13 +920,7 @@
     <t xml:space="preserve">Senior operations Analyst </t>
   </si>
   <si>
-    <t>Analyst</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Quality Assurance engineer </t>
-  </si>
-  <si>
-    <t>Associate Business Analysis</t>
   </si>
   <si>
     <t xml:space="preserve">Software QA engineer </t>
@@ -1402,6 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BI363"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1429,7 +1424,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1603,7 +1598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1788,7 +1783,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1973,7 +1968,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -2155,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -2337,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -2519,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -2701,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -2880,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3059,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -3241,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -3423,7 +3418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -3599,7 +3594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -3610,7 +3605,7 @@
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
@@ -3778,7 +3773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -3960,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -4145,7 +4140,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -4330,7 +4325,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -4509,7 +4504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -4688,7 +4683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -4867,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -5043,7 +5038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -5222,7 +5217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -5401,7 +5396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -5583,7 +5578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -5765,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -5947,7 +5942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -6126,7 +6121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -6308,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -6490,7 +6485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -6675,7 +6670,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -6857,7 +6852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>51</v>
       </c>
@@ -7039,7 +7034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -7224,7 +7219,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>51</v>
       </c>
@@ -7406,7 +7401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -7588,7 +7583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -7770,7 +7765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>51</v>
       </c>
@@ -7952,7 +7947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -8137,7 +8132,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -8319,7 +8314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -8330,7 +8325,7 @@
         <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E39" t="s">
         <v>59</v>
@@ -8501,7 +8496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -8677,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>65</v>
       </c>
@@ -8862,7 +8857,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -9044,7 +9039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>65</v>
       </c>
@@ -9223,7 +9218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -9402,7 +9397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>51</v>
       </c>
@@ -9581,7 +9576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>65</v>
       </c>
@@ -9766,7 +9761,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>65</v>
       </c>
@@ -9948,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -10127,7 +10122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -10306,7 +10301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -10485,7 +10480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -10670,7 +10665,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -10855,7 +10850,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -11037,7 +11032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -11216,7 +11211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -11398,7 +11393,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -11574,7 +11569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -11756,7 +11751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>51</v>
       </c>
@@ -11941,7 +11936,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>51</v>
       </c>
@@ -12120,7 +12115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>51</v>
       </c>
@@ -12302,7 +12297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -12487,7 +12482,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>51</v>
       </c>
@@ -12672,7 +12667,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>51</v>
       </c>
@@ -12851,7 +12846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>51</v>
       </c>
@@ -13030,7 +13025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>51</v>
       </c>
@@ -13212,7 +13207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -13391,7 +13386,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>51</v>
       </c>
@@ -13573,7 +13568,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="68" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>65</v>
       </c>
@@ -13755,7 +13750,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="69" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>51</v>
       </c>
@@ -13937,7 +13932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -14119,7 +14114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>51</v>
       </c>
@@ -14301,7 +14296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>65</v>
       </c>
@@ -14483,7 +14478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>51</v>
       </c>
@@ -15023,7 +15018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>51</v>
       </c>
@@ -15205,7 +15200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>51</v>
       </c>
@@ -15387,7 +15382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>65</v>
       </c>
@@ -15398,7 +15393,7 @@
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E78" t="s">
         <v>69</v>
@@ -15569,7 +15564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>51</v>
       </c>
@@ -15751,7 +15746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>51</v>
       </c>
@@ -15936,7 +15931,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>51</v>
       </c>
@@ -16118,7 +16113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>51</v>
       </c>
@@ -16303,7 +16298,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>51</v>
       </c>
@@ -16485,7 +16480,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>51</v>
       </c>
@@ -16670,7 +16665,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="85" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>51</v>
       </c>
@@ -16849,7 +16844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>51</v>
       </c>
@@ -17031,7 +17026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>51</v>
       </c>
@@ -17216,7 +17211,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>51</v>
       </c>
@@ -17395,7 +17390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>51</v>
       </c>
@@ -17574,7 +17569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>51</v>
       </c>
@@ -17753,7 +17748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>51</v>
       </c>
@@ -17938,7 +17933,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="92" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>51</v>
       </c>
@@ -18120,7 +18115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>51</v>
       </c>
@@ -18299,7 +18294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>65</v>
       </c>
@@ -18481,7 +18476,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="95" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>51</v>
       </c>
@@ -18842,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>51</v>
       </c>
@@ -18853,7 +18848,7 @@
         <v>62</v>
       </c>
       <c r="D97" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E97" t="s">
         <v>67</v>
@@ -19021,7 +19016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>51</v>
       </c>
@@ -19203,7 +19198,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>65</v>
       </c>
@@ -19385,7 +19380,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>51</v>
       </c>
@@ -19567,7 +19562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>51</v>
       </c>
@@ -19752,7 +19747,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>51</v>
       </c>
@@ -19934,7 +19929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>51</v>
       </c>
@@ -20116,7 +20111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>51</v>
       </c>
@@ -20127,7 +20122,7 @@
         <v>62</v>
       </c>
       <c r="D104" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E104" t="s">
         <v>59</v>
@@ -20298,7 +20293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>51</v>
       </c>
@@ -20309,7 +20304,7 @@
         <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E105" t="s">
         <v>59</v>
@@ -20483,7 +20478,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -20494,7 +20489,7 @@
         <v>62</v>
       </c>
       <c r="D106" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
@@ -20665,7 +20660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>51</v>
       </c>
@@ -20850,7 +20845,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>51</v>
       </c>
@@ -21032,7 +21027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>51</v>
       </c>
@@ -21214,7 +21209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>65</v>
       </c>
@@ -21396,7 +21391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>51</v>
       </c>
@@ -21407,7 +21402,7 @@
         <v>62</v>
       </c>
       <c r="D111" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E111" t="s">
         <v>59</v>
@@ -21578,7 +21573,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>51</v>
       </c>
@@ -21763,7 +21758,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="113" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>51</v>
       </c>
@@ -21945,7 +21940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>51</v>
       </c>
@@ -22130,7 +22125,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="115" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>51</v>
       </c>
@@ -22309,7 +22304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>65</v>
       </c>
@@ -22494,7 +22489,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="117" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>51</v>
       </c>
@@ -22679,7 +22674,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="118" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>65</v>
       </c>
@@ -22864,7 +22859,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>51</v>
       </c>
@@ -23046,7 +23041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>65</v>
       </c>
@@ -23228,7 +23223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>65</v>
       </c>
@@ -23410,7 +23405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>51</v>
       </c>
@@ -23595,7 +23590,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>51</v>
       </c>
@@ -23777,7 +23772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>51</v>
       </c>
@@ -23959,7 +23954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>51</v>
       </c>
@@ -24138,7 +24133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>51</v>
       </c>
@@ -24320,7 +24315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>65</v>
       </c>
@@ -24496,7 +24491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>65</v>
       </c>
@@ -24672,7 +24667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>65</v>
       </c>
@@ -24851,7 +24846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>51</v>
       </c>
@@ -25033,7 +25028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>51</v>
       </c>
@@ -25218,7 +25213,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="132" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>51</v>
       </c>
@@ -25397,7 +25392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>51</v>
       </c>
@@ -25579,7 +25574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>65</v>
       </c>
@@ -25755,7 +25750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>65</v>
       </c>
@@ -25934,7 +25929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>51</v>
       </c>
@@ -26116,7 +26111,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="137" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>51</v>
       </c>
@@ -26295,7 +26290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>51</v>
       </c>
@@ -26474,7 +26469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>65</v>
       </c>
@@ -26656,7 +26651,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="140" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>51</v>
       </c>
@@ -26838,7 +26833,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="141" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>51</v>
       </c>
@@ -27020,7 +27015,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="142" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>51</v>
       </c>
@@ -27202,7 +27197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>51</v>
       </c>
@@ -27213,7 +27208,7 @@
         <v>53</v>
       </c>
       <c r="D143" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E143" t="s">
         <v>59</v>
@@ -27384,7 +27379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>65</v>
       </c>
@@ -27566,7 +27561,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="145" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>51</v>
       </c>
@@ -27745,7 +27740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>51</v>
       </c>
@@ -27927,7 +27922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>51</v>
       </c>
@@ -28106,7 +28101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>51</v>
       </c>
@@ -28288,7 +28283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>51</v>
       </c>
@@ -28470,7 +28465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>51</v>
       </c>
@@ -28652,7 +28647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>51</v>
       </c>
@@ -28831,7 +28826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>51</v>
       </c>
@@ -29010,7 +29005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>51</v>
       </c>
@@ -29371,7 +29366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>51</v>
       </c>
@@ -29382,7 +29377,7 @@
         <v>53</v>
       </c>
       <c r="D155" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E155" t="s">
         <v>54</v>
@@ -29553,7 +29548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>65</v>
       </c>
@@ -29735,7 +29730,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="157" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>51</v>
       </c>
@@ -29920,7 +29915,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="158" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>65</v>
       </c>
@@ -30096,7 +30091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>51</v>
       </c>
@@ -30278,7 +30273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>51</v>
       </c>
@@ -30460,7 +30455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>51</v>
       </c>
@@ -30642,7 +30637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>65</v>
       </c>
@@ -30824,7 +30819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>65</v>
       </c>
@@ -31006,7 +31001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>51</v>
       </c>
@@ -31188,7 +31183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>51</v>
       </c>
@@ -31370,7 +31365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>65</v>
       </c>
@@ -31552,7 +31547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>51</v>
       </c>
@@ -31734,7 +31729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>65</v>
       </c>
@@ -31916,7 +31911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>51</v>
       </c>
@@ -32098,7 +32093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>51</v>
       </c>
@@ -32280,7 +32275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>51</v>
       </c>
@@ -32462,7 +32457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>51</v>
       </c>
@@ -32644,7 +32639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>51</v>
       </c>
@@ -32826,7 +32821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>51</v>
       </c>
@@ -33008,7 +33003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>51</v>
       </c>
@@ -33019,7 +33014,7 @@
         <v>62</v>
       </c>
       <c r="D175" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E175" t="s">
         <v>59</v>
@@ -33190,7 +33185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>51</v>
       </c>
@@ -33372,7 +33367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>51</v>
       </c>
@@ -33551,7 +33546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>51</v>
       </c>
@@ -33912,7 +33907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>51</v>
       </c>
@@ -34094,7 +34089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>51</v>
       </c>
@@ -34105,7 +34100,7 @@
         <v>53</v>
       </c>
       <c r="D181" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E181" t="s">
         <v>59</v>
@@ -34276,7 +34271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>51</v>
       </c>
@@ -34458,7 +34453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>51</v>
       </c>
@@ -34640,7 +34635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>51</v>
       </c>
@@ -34822,7 +34817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>51</v>
       </c>
@@ -35004,7 +34999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>51</v>
       </c>
@@ -35197,7 +35192,7 @@
         <v>53</v>
       </c>
       <c r="D187" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E187" t="s">
         <v>59</v>
@@ -35368,7 +35363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>51</v>
       </c>
@@ -35550,7 +35545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>51</v>
       </c>
@@ -35732,7 +35727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>51</v>
       </c>
@@ -35743,7 +35738,7 @@
         <v>62</v>
       </c>
       <c r="D190" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E190" t="s">
         <v>59</v>
@@ -35914,7 +35909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>51</v>
       </c>
@@ -36096,7 +36091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>51</v>
       </c>
@@ -36278,7 +36273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>51</v>
       </c>
@@ -36460,7 +36455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>65</v>
       </c>
@@ -36642,7 +36637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>65</v>
       </c>
@@ -36824,7 +36819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>51</v>
       </c>
@@ -37003,7 +36998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>65</v>
       </c>
@@ -37185,7 +37180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>65</v>
       </c>
@@ -37196,7 +37191,7 @@
         <v>71</v>
       </c>
       <c r="D198" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E198" t="s">
         <v>59</v>
@@ -37367,7 +37362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>51</v>
       </c>
@@ -37546,7 +37541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>65</v>
       </c>
@@ -37722,7 +37717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>51</v>
       </c>
@@ -37901,7 +37896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>51</v>
       </c>
@@ -38077,7 +38072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>51</v>
       </c>
@@ -38259,7 +38254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>51</v>
       </c>
@@ -38270,7 +38265,7 @@
         <v>62</v>
       </c>
       <c r="D204" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E204" t="s">
         <v>59</v>
@@ -38441,7 +38436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>51</v>
       </c>
@@ -38623,7 +38618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>51</v>
       </c>
@@ -38805,7 +38800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>51</v>
       </c>
@@ -38816,7 +38811,7 @@
         <v>53</v>
       </c>
       <c r="D207" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E207" t="s">
         <v>59</v>
@@ -38987,7 +38982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>51</v>
       </c>
@@ -39351,7 +39346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>51</v>
       </c>
@@ -39530,7 +39525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>51</v>
       </c>
@@ -39712,7 +39707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>51</v>
       </c>
@@ -39891,7 +39886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>51</v>
       </c>
@@ -40073,7 +40068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>51</v>
       </c>
@@ -40252,7 +40247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>51</v>
       </c>
@@ -40434,7 +40429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>51</v>
       </c>
@@ -40610,7 +40605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>51</v>
       </c>
@@ -40789,7 +40784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>51</v>
       </c>
@@ -41153,7 +41148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>51</v>
       </c>
@@ -41164,7 +41159,7 @@
         <v>71</v>
       </c>
       <c r="D220" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E220" t="s">
         <v>59</v>
@@ -41335,7 +41330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>51</v>
       </c>
@@ -41699,7 +41694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>51</v>
       </c>
@@ -41878,7 +41873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>65</v>
       </c>
@@ -42060,7 +42055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>51</v>
       </c>
@@ -42242,7 +42237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>51</v>
       </c>
@@ -42424,7 +42419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>51</v>
       </c>
@@ -42606,7 +42601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>51</v>
       </c>
@@ -42788,7 +42783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>65</v>
       </c>
@@ -42964,7 +42959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>51</v>
       </c>
@@ -43146,7 +43141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>65</v>
       </c>
@@ -43328,7 +43323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>65</v>
       </c>
@@ -43510,7 +43505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>51</v>
       </c>
@@ -43689,7 +43684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>51</v>
       </c>
@@ -43700,7 +43695,7 @@
         <v>71</v>
       </c>
       <c r="D234" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E234" t="s">
         <v>54</v>
@@ -43871,7 +43866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>51</v>
       </c>
@@ -44053,7 +44048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>51</v>
       </c>
@@ -44235,7 +44230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>65</v>
       </c>
@@ -44417,7 +44412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>51</v>
       </c>
@@ -44596,7 +44591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>65</v>
       </c>
@@ -44778,7 +44773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>51</v>
       </c>
@@ -45136,7 +45131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>51</v>
       </c>
@@ -45147,7 +45142,7 @@
         <v>71</v>
       </c>
       <c r="D242" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E242" t="s">
         <v>59</v>
@@ -45318,7 +45313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>51</v>
       </c>
@@ -45500,7 +45495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>51</v>
       </c>
@@ -45679,7 +45674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>51</v>
       </c>
@@ -45861,7 +45856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>65</v>
       </c>
@@ -46043,7 +46038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>51</v>
       </c>
@@ -46225,7 +46220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>65</v>
       </c>
@@ -46407,7 +46402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>65</v>
       </c>
@@ -46418,7 +46413,7 @@
         <v>75</v>
       </c>
       <c r="D249" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E249" t="s">
         <v>59</v>
@@ -46589,7 +46584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>51</v>
       </c>
@@ -46771,7 +46766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>51</v>
       </c>
@@ -46950,7 +46945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>65</v>
       </c>
@@ -47132,7 +47127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>51</v>
       </c>
@@ -47314,7 +47309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>51</v>
       </c>
@@ -47325,7 +47320,7 @@
         <v>62</v>
       </c>
       <c r="D254" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E254" t="s">
         <v>59</v>
@@ -47496,7 +47491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>65</v>
       </c>
@@ -47678,7 +47673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>51</v>
       </c>
@@ -48042,7 +48037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>65</v>
       </c>
@@ -48224,7 +48219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>65</v>
       </c>
@@ -48585,7 +48580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>51</v>
       </c>
@@ -48596,7 +48591,7 @@
         <v>53</v>
       </c>
       <c r="D261" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E261" t="s">
         <v>59</v>
@@ -48764,7 +48759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>51</v>
       </c>
@@ -48943,7 +48938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>51</v>
       </c>
@@ -49122,7 +49117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>51</v>
       </c>
@@ -49133,7 +49128,7 @@
         <v>71</v>
       </c>
       <c r="D264" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E264" t="s">
         <v>59</v>
@@ -49486,7 +49481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>51</v>
       </c>
@@ -49665,7 +49660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>51</v>
       </c>
@@ -49858,7 +49853,7 @@
         <v>71</v>
       </c>
       <c r="D268" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E268" t="s">
         <v>59</v>
@@ -50029,7 +50024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>65</v>
       </c>
@@ -50211,7 +50206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>51</v>
       </c>
@@ -50393,7 +50388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>51</v>
       </c>
@@ -50575,7 +50570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>51</v>
       </c>
@@ -50936,7 +50931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>51</v>
       </c>
@@ -51118,7 +51113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>65</v>
       </c>
@@ -51300,7 +51295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>51</v>
       </c>
@@ -51476,7 +51471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>51</v>
       </c>
@@ -51658,7 +51653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>65</v>
       </c>
@@ -52016,7 +52011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>51</v>
       </c>
@@ -52195,7 +52190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>65</v>
       </c>
@@ -52377,7 +52372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>65</v>
       </c>
@@ -52559,7 +52554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>51</v>
       </c>
@@ -52741,7 +52736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>65</v>
       </c>
@@ -52923,7 +52918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>51</v>
       </c>
@@ -52934,7 +52929,7 @@
         <v>53</v>
       </c>
       <c r="D285" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E285" t="s">
         <v>59</v>
@@ -53105,7 +53100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>51</v>
       </c>
@@ -53116,7 +53111,7 @@
         <v>53</v>
       </c>
       <c r="D286" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E286" t="s">
         <v>67</v>
@@ -53287,7 +53282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>51</v>
       </c>
@@ -53651,7 +53646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>51</v>
       </c>
@@ -53833,7 +53828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>65</v>
       </c>
@@ -54015,7 +54010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>51</v>
       </c>
@@ -54564,7 +54559,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="294" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>51</v>
       </c>
@@ -54575,7 +54570,7 @@
         <v>53</v>
       </c>
       <c r="D294" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E294" t="s">
         <v>54</v>
@@ -55107,7 +55102,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="297" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>51</v>
       </c>
@@ -55289,7 +55284,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="298" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>51</v>
       </c>
@@ -55300,7 +55295,7 @@
         <v>53</v>
       </c>
       <c r="D298" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E298" t="s">
         <v>67</v>
@@ -55471,7 +55466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>51</v>
       </c>
@@ -55482,7 +55477,7 @@
         <v>53</v>
       </c>
       <c r="D299" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E299" t="s">
         <v>67</v>
@@ -55653,7 +55648,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="300" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>51</v>
       </c>
@@ -55664,7 +55659,7 @@
         <v>53</v>
       </c>
       <c r="D300" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E300" t="s">
         <v>59</v>
@@ -55835,7 +55830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>51</v>
       </c>
@@ -56017,7 +56012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>65</v>
       </c>
@@ -56199,7 +56194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>51</v>
       </c>
@@ -56381,7 +56376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>51</v>
       </c>
@@ -56392,7 +56387,7 @@
         <v>71</v>
       </c>
       <c r="D304" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E304" t="s">
         <v>59</v>
@@ -56563,7 +56558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>51</v>
       </c>
@@ -56745,7 +56740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>65</v>
       </c>
@@ -56927,7 +56922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>51</v>
       </c>
@@ -57112,7 +57107,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="308" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>65</v>
       </c>
@@ -57291,7 +57286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>65</v>
       </c>
@@ -57473,7 +57468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>65</v>
       </c>
@@ -57655,7 +57650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>51</v>
       </c>
@@ -58013,7 +58008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>51</v>
       </c>
@@ -58195,7 +58190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>51</v>
       </c>
@@ -58374,7 +58369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>51</v>
       </c>
@@ -58735,7 +58730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>65</v>
       </c>
@@ -58746,7 +58741,7 @@
         <v>71</v>
       </c>
       <c r="D317" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E317" t="s">
         <v>59</v>
@@ -58917,7 +58912,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="318" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>51</v>
       </c>
@@ -59099,7 +59094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>65</v>
       </c>
@@ -59460,7 +59455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>51</v>
       </c>
@@ -59639,7 +59634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>65</v>
       </c>
@@ -59821,7 +59816,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="323" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>51</v>
       </c>
@@ -60003,7 +59998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>51</v>
       </c>
@@ -60185,7 +60180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>65</v>
       </c>
@@ -60731,7 +60726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>51</v>
       </c>
@@ -60916,7 +60911,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="329" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>51</v>
       </c>
@@ -61109,7 +61104,7 @@
         <v>71</v>
       </c>
       <c r="D330" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E330" t="s">
         <v>67</v>
@@ -61283,7 +61278,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="331" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>51</v>
       </c>
@@ -61465,7 +61460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>65</v>
       </c>
@@ -61476,7 +61471,7 @@
         <v>75</v>
       </c>
       <c r="D332" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E332" t="s">
         <v>67</v>
@@ -61647,7 +61642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>65</v>
       </c>
@@ -61823,7 +61818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>65</v>
       </c>
@@ -61834,7 +61829,7 @@
         <v>71</v>
       </c>
       <c r="D334" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E334" t="s">
         <v>59</v>
@@ -62008,7 +62003,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="335" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>65</v>
       </c>
@@ -62193,7 +62188,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="336" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>65</v>
       </c>
@@ -62375,7 +62370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>65</v>
       </c>
@@ -62557,7 +62552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>65</v>
       </c>
@@ -63103,7 +63098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>65</v>
       </c>
@@ -63279,7 +63274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>51</v>
       </c>
@@ -63455,7 +63450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>65</v>
       </c>
@@ -63637,7 +63632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>65</v>
       </c>
@@ -63819,7 +63814,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="345" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>51</v>
       </c>
@@ -63830,7 +63825,7 @@
         <v>53</v>
       </c>
       <c r="D345" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E345" t="s">
         <v>59</v>
@@ -64004,7 +63999,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="346" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>51</v>
       </c>
@@ -64371,7 +64366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>51</v>
       </c>
@@ -64553,7 +64548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>51</v>
       </c>
@@ -64735,7 +64730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>65</v>
       </c>
@@ -65107,7 +65102,7 @@
         <v>71</v>
       </c>
       <c r="D352" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="E352" t="s">
         <v>54</v>
@@ -65281,7 +65276,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="353" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>65</v>
       </c>
@@ -65292,7 +65287,7 @@
         <v>71</v>
       </c>
       <c r="D353" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E353" t="s">
         <v>59</v>
@@ -65474,7 +65469,7 @@
         <v>71</v>
       </c>
       <c r="D354" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="E354" t="s">
         <v>59</v>
@@ -65645,7 +65640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>65</v>
       </c>
@@ -65656,7 +65651,7 @@
         <v>71</v>
       </c>
       <c r="D355" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E355" t="s">
         <v>59</v>
@@ -65827,7 +65822,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="356" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>65</v>
       </c>
@@ -65838,7 +65833,7 @@
         <v>75</v>
       </c>
       <c r="D356" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E356" t="s">
         <v>54</v>
@@ -66009,7 +66004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>65</v>
       </c>
@@ -66020,7 +66015,7 @@
         <v>71</v>
       </c>
       <c r="D357" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E357" t="s">
         <v>59</v>
@@ -66194,7 +66189,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="358" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>51</v>
       </c>
@@ -66379,7 +66374,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="359" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>65</v>
       </c>
@@ -66390,7 +66385,7 @@
         <v>75</v>
       </c>
       <c r="D359" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E359" t="s">
         <v>69</v>
@@ -66564,7 +66559,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="360" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>65</v>
       </c>
@@ -66746,7 +66741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>65</v>
       </c>
@@ -66931,7 +66926,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="362" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>65</v>
       </c>
@@ -67113,7 +67108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>65</v>
       </c>
@@ -67296,7 +67291,37 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI363" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BI363" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Analyst"/>
+        <filter val="Assistant Application Analyst"/>
+        <filter val="assistant data analyst"/>
+        <filter val="Associate Business Analysis"/>
+        <filter val="associate Business Analyst"/>
+        <filter val="Associate Operations Analyst"/>
+        <filter val="Business Analyst"/>
+        <filter val="business analyst Intern"/>
+        <filter val="Data Analyst"/>
+        <filter val="Deputy Analyst"/>
+        <filter val="Digital Marketing Analyst"/>
+        <filter val="Intern Business analyst"/>
+        <filter val="Junior Executive Advance Analytics &amp; Data Translator"/>
+        <filter val="Logistic Analyst"/>
+        <filter val="Material Analyst"/>
+        <filter val="Operation Analyst"/>
+        <filter val="Operations Analysist"/>
+        <filter val="Operations Analyst"/>
+        <filter val="Opertions Analyst"/>
+        <filter val="Price Analyst"/>
+        <filter val="Product Analyst"/>
+        <filter val="Quality assurance Analyst"/>
+        <filter val="Regional Accuracy Analyst"/>
+        <filter val="Senior operations Analyst"/>
+        <filter val="Supply chain Analyst"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/final_data2.xlsx
+++ b/data/final_data2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive\CMIS 4†26 - Project\Data Set\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7344F006-EBEC-49AA-B6B2-6F56D144A98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872936D4-68B2-43ED-A7FA-4D7813E90E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="329">
   <si>
     <t>Type of Degree</t>
   </si>
@@ -776,9 +776,6 @@
     <t>Train Controlling Technical Assistant</t>
   </si>
   <si>
-    <t>Junior Qulity Assurance Engineer</t>
-  </si>
-  <si>
     <t>Work Study Assistant</t>
   </si>
   <si>
@@ -1424,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -3605,7 +3602,7 @@
         <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
@@ -8325,7 +8322,7 @@
         <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E39" t="s">
         <v>59</v>
@@ -14660,7 +14657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>65</v>
       </c>
@@ -14671,7 +14668,7 @@
         <v>71</v>
       </c>
       <c r="D74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E74" t="s">
         <v>59</v>
@@ -14839,7 +14836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>65</v>
       </c>
@@ -15393,7 +15390,7 @@
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E78" t="s">
         <v>69</v>
@@ -18658,7 +18655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>65</v>
       </c>
@@ -18848,7 +18845,7 @@
         <v>62</v>
       </c>
       <c r="D97" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E97" t="s">
         <v>67</v>
@@ -20122,7 +20119,7 @@
         <v>62</v>
       </c>
       <c r="D104" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E104" t="s">
         <v>59</v>
@@ -20304,7 +20301,7 @@
         <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E105" t="s">
         <v>59</v>
@@ -20489,7 +20486,7 @@
         <v>62</v>
       </c>
       <c r="D106" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
@@ -21402,7 +21399,7 @@
         <v>62</v>
       </c>
       <c r="D111" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E111" t="s">
         <v>59</v>
@@ -27208,7 +27205,7 @@
         <v>53</v>
       </c>
       <c r="D143" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E143" t="s">
         <v>59</v>
@@ -28465,7 +28462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>51</v>
       </c>
@@ -29184,7 +29181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>51</v>
       </c>
@@ -29377,7 +29374,7 @@
         <v>53</v>
       </c>
       <c r="D155" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E155" t="s">
         <v>54</v>
@@ -33014,7 +33011,7 @@
         <v>62</v>
       </c>
       <c r="D175" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E175" t="s">
         <v>59</v>
@@ -33546,7 +33543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>51</v>
       </c>
@@ -33728,7 +33725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>65</v>
       </c>
@@ -34089,7 +34086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>51</v>
       </c>
@@ -34100,7 +34097,7 @@
         <v>53</v>
       </c>
       <c r="D181" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E181" t="s">
         <v>59</v>
@@ -35181,7 +35178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>51</v>
       </c>
@@ -35192,7 +35189,7 @@
         <v>53</v>
       </c>
       <c r="D187" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E187" t="s">
         <v>59</v>
@@ -35738,7 +35735,7 @@
         <v>62</v>
       </c>
       <c r="D190" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E190" t="s">
         <v>59</v>
@@ -37191,7 +37188,7 @@
         <v>71</v>
       </c>
       <c r="D198" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E198" t="s">
         <v>59</v>
@@ -37362,7 +37359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>51</v>
       </c>
@@ -38265,7 +38262,7 @@
         <v>62</v>
       </c>
       <c r="D204" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E204" t="s">
         <v>59</v>
@@ -38811,7 +38808,7 @@
         <v>53</v>
       </c>
       <c r="D207" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E207" t="s">
         <v>59</v>
@@ -39164,7 +39161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>51</v>
       </c>
@@ -40966,7 +40963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>51</v>
       </c>
@@ -41159,7 +41156,7 @@
         <v>71</v>
       </c>
       <c r="D220" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E220" t="s">
         <v>59</v>
@@ -41512,7 +41509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>65</v>
       </c>
@@ -42959,7 +42956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>51</v>
       </c>
@@ -42970,7 +42967,7 @@
         <v>53</v>
       </c>
       <c r="D230" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="E230" t="s">
         <v>59</v>
@@ -43516,7 +43513,7 @@
         <v>53</v>
       </c>
       <c r="D233" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E233" t="s">
         <v>59</v>
@@ -43695,7 +43692,7 @@
         <v>71</v>
       </c>
       <c r="D234" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E234" t="s">
         <v>54</v>
@@ -43877,7 +43874,7 @@
         <v>53</v>
       </c>
       <c r="D235" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E235" t="s">
         <v>59</v>
@@ -44773,7 +44770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>51</v>
       </c>
@@ -44952,7 +44949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>51</v>
       </c>
@@ -44963,7 +44960,7 @@
         <v>71</v>
       </c>
       <c r="D241" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E241" t="s">
         <v>59</v>
@@ -45142,7 +45139,7 @@
         <v>71</v>
       </c>
       <c r="D242" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E242" t="s">
         <v>59</v>
@@ -45324,7 +45321,7 @@
         <v>53</v>
       </c>
       <c r="D243" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E243" t="s">
         <v>59</v>
@@ -46413,7 +46410,7 @@
         <v>75</v>
       </c>
       <c r="D249" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E249" t="s">
         <v>59</v>
@@ -46777,7 +46774,7 @@
         <v>53</v>
       </c>
       <c r="D251" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E251" t="s">
         <v>59</v>
@@ -47320,7 +47317,7 @@
         <v>62</v>
       </c>
       <c r="D254" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E254" t="s">
         <v>59</v>
@@ -47502,7 +47499,7 @@
         <v>71</v>
       </c>
       <c r="D255" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E255" t="s">
         <v>59</v>
@@ -47684,7 +47681,7 @@
         <v>71</v>
       </c>
       <c r="D256" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E256" t="s">
         <v>59</v>
@@ -47855,7 +47852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>65</v>
       </c>
@@ -47866,7 +47863,7 @@
         <v>71</v>
       </c>
       <c r="D257" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E257" t="s">
         <v>59</v>
@@ -48230,7 +48227,7 @@
         <v>71</v>
       </c>
       <c r="D259" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E259" t="s">
         <v>59</v>
@@ -48401,7 +48398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>51</v>
       </c>
@@ -48412,7 +48409,7 @@
         <v>62</v>
       </c>
       <c r="D260" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E260" t="s">
         <v>59</v>
@@ -48591,7 +48588,7 @@
         <v>53</v>
       </c>
       <c r="D261" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E261" t="s">
         <v>59</v>
@@ -49128,7 +49125,7 @@
         <v>71</v>
       </c>
       <c r="D264" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E264" t="s">
         <v>59</v>
@@ -49299,7 +49296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>51</v>
       </c>
@@ -49310,7 +49307,7 @@
         <v>62</v>
       </c>
       <c r="D265" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E265" t="s">
         <v>67</v>
@@ -49492,7 +49489,7 @@
         <v>62</v>
       </c>
       <c r="D266" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E266" t="s">
         <v>59</v>
@@ -49842,7 +49839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>51</v>
       </c>
@@ -49853,7 +49850,7 @@
         <v>71</v>
       </c>
       <c r="D268" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E268" t="s">
         <v>59</v>
@@ -50217,7 +50214,7 @@
         <v>62</v>
       </c>
       <c r="D270" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E270" t="s">
         <v>67</v>
@@ -50749,7 +50746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>65</v>
       </c>
@@ -50760,7 +50757,7 @@
         <v>71</v>
       </c>
       <c r="D273" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E273" t="s">
         <v>59</v>
@@ -50942,7 +50939,7 @@
         <v>53</v>
       </c>
       <c r="D274" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E274" t="s">
         <v>59</v>
@@ -51306,7 +51303,7 @@
         <v>62</v>
       </c>
       <c r="D276" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E276" t="s">
         <v>59</v>
@@ -51832,7 +51829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>51</v>
       </c>
@@ -52022,7 +52019,7 @@
         <v>53</v>
       </c>
       <c r="D280" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E280" t="s">
         <v>59</v>
@@ -52929,7 +52926,7 @@
         <v>53</v>
       </c>
       <c r="D285" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E285" t="s">
         <v>59</v>
@@ -53111,7 +53108,7 @@
         <v>53</v>
       </c>
       <c r="D286" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E286" t="s">
         <v>67</v>
@@ -53293,7 +53290,7 @@
         <v>53</v>
       </c>
       <c r="D287" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E287" t="s">
         <v>54</v>
@@ -53464,7 +53461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>51</v>
       </c>
@@ -53475,7 +53472,7 @@
         <v>53</v>
       </c>
       <c r="D288" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E288" t="s">
         <v>59</v>
@@ -54192,7 +54189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>51</v>
       </c>
@@ -54203,7 +54200,7 @@
         <v>71</v>
       </c>
       <c r="D292" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E292" t="s">
         <v>54</v>
@@ -54374,7 +54371,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="293" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>65</v>
       </c>
@@ -54385,7 +54382,7 @@
         <v>53</v>
       </c>
       <c r="D293" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E293" t="s">
         <v>59</v>
@@ -54570,7 +54567,7 @@
         <v>53</v>
       </c>
       <c r="D294" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E294" t="s">
         <v>54</v>
@@ -54741,7 +54738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>51</v>
       </c>
@@ -54752,7 +54749,7 @@
         <v>53</v>
       </c>
       <c r="D295" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E295" t="s">
         <v>59</v>
@@ -54920,7 +54917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>51</v>
       </c>
@@ -55113,7 +55110,7 @@
         <v>53</v>
       </c>
       <c r="D297" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E297" t="s">
         <v>59</v>
@@ -55295,7 +55292,7 @@
         <v>53</v>
       </c>
       <c r="D298" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E298" t="s">
         <v>67</v>
@@ -55466,7 +55463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>51</v>
       </c>
@@ -55477,7 +55474,7 @@
         <v>53</v>
       </c>
       <c r="D299" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E299" t="s">
         <v>67</v>
@@ -55648,7 +55645,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="300" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>51</v>
       </c>
@@ -55659,7 +55656,7 @@
         <v>53</v>
       </c>
       <c r="D300" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E300" t="s">
         <v>59</v>
@@ -55841,7 +55838,7 @@
         <v>53</v>
       </c>
       <c r="D301" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E301" t="s">
         <v>59</v>
@@ -56194,7 +56191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>51</v>
       </c>
@@ -56387,7 +56384,7 @@
         <v>71</v>
       </c>
       <c r="D304" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E304" t="s">
         <v>59</v>
@@ -56569,7 +56566,7 @@
         <v>53</v>
       </c>
       <c r="D305" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E305" t="s">
         <v>67</v>
@@ -56740,7 +56737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>65</v>
       </c>
@@ -56751,7 +56748,7 @@
         <v>71</v>
       </c>
       <c r="D306" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E306" t="s">
         <v>59</v>
@@ -56933,7 +56930,7 @@
         <v>71</v>
       </c>
       <c r="D307" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E307" t="s">
         <v>59</v>
@@ -57832,7 +57829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>51</v>
       </c>
@@ -57843,7 +57840,7 @@
         <v>53</v>
       </c>
       <c r="D312" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E312" t="s">
         <v>54</v>
@@ -58019,7 +58016,7 @@
         <v>53</v>
       </c>
       <c r="D313" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E313" t="s">
         <v>59</v>
@@ -58190,7 +58187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>51</v>
       </c>
@@ -58551,7 +58548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>65</v>
       </c>
@@ -58562,7 +58559,7 @@
         <v>71</v>
       </c>
       <c r="D316" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E316" t="s">
         <v>59</v>
@@ -58741,7 +58738,7 @@
         <v>71</v>
       </c>
       <c r="D317" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E317" t="s">
         <v>59</v>
@@ -59105,7 +59102,7 @@
         <v>71</v>
       </c>
       <c r="D319" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E319" t="s">
         <v>59</v>
@@ -59276,7 +59273,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="320" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>51</v>
       </c>
@@ -59287,7 +59284,7 @@
         <v>53</v>
       </c>
       <c r="D320" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E320" t="s">
         <v>59</v>
@@ -59466,7 +59463,7 @@
         <v>53</v>
       </c>
       <c r="D321" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E321" t="s">
         <v>59</v>
@@ -59634,7 +59631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>65</v>
       </c>
@@ -59645,7 +59642,7 @@
         <v>71</v>
       </c>
       <c r="D322" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E322" t="s">
         <v>54</v>
@@ -60009,7 +60006,7 @@
         <v>53</v>
       </c>
       <c r="D324" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E324" t="s">
         <v>54</v>
@@ -60191,7 +60188,7 @@
         <v>71</v>
       </c>
       <c r="D325" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E325" t="s">
         <v>59</v>
@@ -60362,7 +60359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>51</v>
       </c>
@@ -60373,7 +60370,7 @@
         <v>53</v>
       </c>
       <c r="D326" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E326" t="s">
         <v>59</v>
@@ -60544,7 +60541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>51</v>
       </c>
@@ -60555,7 +60552,7 @@
         <v>53</v>
       </c>
       <c r="D327" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E327" t="s">
         <v>59</v>
@@ -60737,7 +60734,7 @@
         <v>71</v>
       </c>
       <c r="D328" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E328" t="s">
         <v>59</v>
@@ -60922,7 +60919,7 @@
         <v>53</v>
       </c>
       <c r="D329" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E329" t="s">
         <v>59</v>
@@ -61093,7 +61090,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="330" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>51</v>
       </c>
@@ -61104,7 +61101,7 @@
         <v>71</v>
       </c>
       <c r="D330" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E330" t="s">
         <v>67</v>
@@ -61471,7 +61468,7 @@
         <v>75</v>
       </c>
       <c r="D332" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E332" t="s">
         <v>67</v>
@@ -61642,7 +61639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>65</v>
       </c>
@@ -61653,7 +61650,7 @@
         <v>71</v>
       </c>
       <c r="D333" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E333" t="s">
         <v>54</v>
@@ -61829,7 +61826,7 @@
         <v>71</v>
       </c>
       <c r="D334" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E334" t="s">
         <v>59</v>
@@ -62188,7 +62185,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="336" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>65</v>
       </c>
@@ -62199,7 +62196,7 @@
         <v>71</v>
       </c>
       <c r="D336" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E336" t="s">
         <v>59</v>
@@ -62381,7 +62378,7 @@
         <v>71</v>
       </c>
       <c r="D337" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E337" t="s">
         <v>69</v>
@@ -62563,7 +62560,7 @@
         <v>71</v>
       </c>
       <c r="D338" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E338" t="s">
         <v>59</v>
@@ -62734,7 +62731,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="339" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>51</v>
       </c>
@@ -62745,7 +62742,7 @@
         <v>53</v>
       </c>
       <c r="D339" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E339" t="s">
         <v>59</v>
@@ -62916,7 +62913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>51</v>
       </c>
@@ -62927,7 +62924,7 @@
         <v>53</v>
       </c>
       <c r="D340" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E340" t="s">
         <v>59</v>
@@ -63285,7 +63282,7 @@
         <v>53</v>
       </c>
       <c r="D342" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E342" t="s">
         <v>54</v>
@@ -63461,7 +63458,7 @@
         <v>71</v>
       </c>
       <c r="D343" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E343" t="s">
         <v>59</v>
@@ -63643,7 +63640,7 @@
         <v>71</v>
       </c>
       <c r="D344" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E344" t="s">
         <v>59</v>
@@ -63825,7 +63822,7 @@
         <v>53</v>
       </c>
       <c r="D345" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E345" t="s">
         <v>59</v>
@@ -64195,7 +64192,7 @@
         <v>71</v>
       </c>
       <c r="D347" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E347" t="s">
         <v>59</v>
@@ -64915,7 +64912,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="351" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>65</v>
       </c>
@@ -64926,7 +64923,7 @@
         <v>71</v>
       </c>
       <c r="D351" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E351" t="s">
         <v>59</v>
@@ -65091,7 +65088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>51</v>
       </c>
@@ -65102,7 +65099,7 @@
         <v>71</v>
       </c>
       <c r="D352" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E352" t="s">
         <v>54</v>
@@ -65276,7 +65273,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="353" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>65</v>
       </c>
@@ -65287,7 +65284,7 @@
         <v>71</v>
       </c>
       <c r="D353" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E353" t="s">
         <v>59</v>
@@ -65458,7 +65455,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="354" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:61" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>51</v>
       </c>
@@ -65469,7 +65466,7 @@
         <v>71</v>
       </c>
       <c r="D354" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E354" t="s">
         <v>59</v>
@@ -65651,7 +65648,7 @@
         <v>71</v>
       </c>
       <c r="D355" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E355" t="s">
         <v>59</v>
@@ -65833,7 +65830,7 @@
         <v>75</v>
       </c>
       <c r="D356" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E356" t="s">
         <v>54</v>
@@ -66015,7 +66012,7 @@
         <v>71</v>
       </c>
       <c r="D357" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E357" t="s">
         <v>59</v>
@@ -66385,7 +66382,7 @@
         <v>75</v>
       </c>
       <c r="D359" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E359" t="s">
         <v>69</v>
@@ -67294,31 +67291,16 @@
   <autoFilter ref="A1:BI363" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="3">
       <filters>
-        <filter val="Analyst"/>
-        <filter val="Assistant Application Analyst"/>
-        <filter val="assistant data analyst"/>
-        <filter val="Associate Business Analysis"/>
-        <filter val="associate Business Analyst"/>
-        <filter val="Associate Operations Analyst"/>
-        <filter val="Business Analyst"/>
-        <filter val="business analyst Intern"/>
-        <filter val="Data Analyst"/>
-        <filter val="Deputy Analyst"/>
-        <filter val="Digital Marketing Analyst"/>
-        <filter val="Intern Business analyst"/>
-        <filter val="Junior Executive Advance Analytics &amp; Data Translator"/>
-        <filter val="Logistic Analyst"/>
-        <filter val="Material Analyst"/>
-        <filter val="Operation Analyst"/>
-        <filter val="Operations Analysist"/>
-        <filter val="Operations Analyst"/>
-        <filter val="Opertions Analyst"/>
-        <filter val="Price Analyst"/>
-        <filter val="Product Analyst"/>
+        <filter val="Associate Quality Assouance Engineer"/>
+        <filter val="Associate Quality Assurance Engineer"/>
+        <filter val="intern Quality Engineering"/>
+        <filter val="intern software Quality engineer"/>
+        <filter val="Junior Quality Assurance engineer"/>
+        <filter val="Junior Qulity Assurance Engineer"/>
         <filter val="Quality assurance Analyst"/>
-        <filter val="Regional Accuracy Analyst"/>
-        <filter val="Senior operations Analyst"/>
-        <filter val="Supply chain Analyst"/>
+        <filter val="Quality Assurance Technologist"/>
+        <filter val="Quality Executive"/>
+        <filter val="Software Quality Assurance Engineer"/>
       </filters>
     </filterColumn>
   </autoFilter>
